--- a/public/assets/templates/maintenance/electric_engine.xlsx
+++ b/public/assets/templates/maintenance/electric_engine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722EFE4B-2119-499A-B384-9B120FD2E1AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17AD7346-7B9E-4F64-B6A4-5D671C6F910A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{7A80608D-5162-4C69-AACA-06EF8CFA5F02}"/>
   </bookViews>
@@ -657,16 +657,13 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -721,18 +718,24 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -829,18 +832,45 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -864,33 +894,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1262,1082 +1265,1082 @@
   <dimension ref="A1:M83"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11" style="24" customWidth="1"/>
-    <col min="2" max="2" width="3" style="24" customWidth="1"/>
-    <col min="3" max="3" width="4.26953125" style="24" customWidth="1"/>
-    <col min="4" max="4" width="24.26953125" style="24" customWidth="1"/>
-    <col min="5" max="5" width="6.26953125" style="24" customWidth="1"/>
-    <col min="6" max="6" width="2.26953125" style="24" customWidth="1"/>
-    <col min="7" max="7" width="18.90625" style="24" customWidth="1"/>
-    <col min="8" max="8" width="4.7265625" style="24" customWidth="1"/>
-    <col min="9" max="9" width="6" style="24" customWidth="1"/>
+    <col min="1" max="1" width="11" style="21" customWidth="1"/>
+    <col min="2" max="2" width="3" style="21" customWidth="1"/>
+    <col min="3" max="3" width="4.26953125" style="21" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" style="21" customWidth="1"/>
+    <col min="5" max="5" width="6.26953125" style="21" customWidth="1"/>
+    <col min="6" max="6" width="2.26953125" style="21" customWidth="1"/>
+    <col min="7" max="7" width="18.90625" style="21" customWidth="1"/>
+    <col min="8" max="8" width="4.7265625" style="21" customWidth="1"/>
+    <col min="9" max="9" width="6" style="21" customWidth="1"/>
     <col min="13" max="13" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" thickTop="1">
-      <c r="A1" s="70"/>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="74" t="s">
+      <c r="A1" s="63"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="75"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="68"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="76" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="77"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="70"/>
     </row>
     <row r="3" spans="1:13" ht="10" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="62" t="s">
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="63"/>
-      <c r="G3" s="64" t="s">
+      <c r="F3" s="73"/>
+      <c r="G3" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="65"/>
-      <c r="I3" s="66"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="76"/>
     </row>
     <row r="4" spans="1:13" ht="10" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="61"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="62" t="s">
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="63"/>
-      <c r="G4" s="64" t="s">
+      <c r="F4" s="73"/>
+      <c r="G4" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="65"/>
-      <c r="I4" s="66"/>
-    </row>
-    <row r="5" spans="1:13" s="6" customFormat="1" ht="11" customHeight="1">
-      <c r="A5" s="3" t="s">
+      <c r="H4" s="75"/>
+      <c r="I4" s="76"/>
+    </row>
+    <row r="5" spans="1:13" s="5" customFormat="1" ht="11" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="67" t="s">
+      <c r="B5" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="4" t="s">
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="45" t="s">
+      <c r="F5" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="68"/>
-    </row>
-    <row r="6" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
-      <c r="A6" s="69" t="s">
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="78"/>
+    </row>
+    <row r="6" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A6" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="27"/>
-    </row>
-    <row r="7" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
-      <c r="A7" s="69"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="E6" s="22"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="28"/>
+    </row>
+    <row r="7" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A7" s="62"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="27"/>
-    </row>
-    <row r="8" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
-      <c r="A8" s="69"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="E7" s="22"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="28"/>
+    </row>
+    <row r="8" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A8" s="62"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="27"/>
-    </row>
-    <row r="9" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
-      <c r="A9" s="69"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E8" s="22"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="28"/>
+    </row>
+    <row r="9" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A9" s="62"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="27"/>
-    </row>
-    <row r="10" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
-      <c r="A10" s="69"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="E9" s="22"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="28"/>
+    </row>
+    <row r="10" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A10" s="62"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="27"/>
-    </row>
-    <row r="11" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
-      <c r="A11" s="69"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="E10" s="22"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="28"/>
+    </row>
+    <row r="11" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A11" s="62"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="27"/>
-    </row>
-    <row r="12" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
-      <c r="A12" s="69"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="E11" s="22"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="28"/>
+    </row>
+    <row r="12" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A12" s="62"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="27"/>
-    </row>
-    <row r="13" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
-      <c r="A13" s="69"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="E12" s="22"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="28"/>
+    </row>
+    <row r="13" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A13" s="62"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="27"/>
-    </row>
-    <row r="14" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
-      <c r="A14" s="69"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="27"/>
-    </row>
-    <row r="15" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
-      <c r="A15" s="69"/>
-      <c r="B15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="27"/>
-    </row>
-    <row r="16" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E13" s="22"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="28"/>
+    </row>
+    <row r="14" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A14" s="62"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="28"/>
+    </row>
+    <row r="15" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A15" s="62"/>
+      <c r="B15" s="6"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="28"/>
+    </row>
+    <row r="16" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A16" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="11" t="s">
+      <c r="B16" s="6"/>
+      <c r="C16" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="27"/>
-      <c r="L16" s="59"/>
-      <c r="M16" s="59"/>
-    </row>
-    <row r="17" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E16" s="22"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="28"/>
+      <c r="L16" s="60"/>
+      <c r="M16" s="60"/>
+    </row>
+    <row r="17" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A17" s="58"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="9" t="s">
+      <c r="B17" s="6"/>
+      <c r="C17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="27"/>
-      <c r="L17" s="60"/>
-      <c r="M17" s="60"/>
-    </row>
-    <row r="18" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E17" s="22"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="28"/>
+      <c r="L17" s="61"/>
+      <c r="M17" s="61"/>
+    </row>
+    <row r="18" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A18" s="58"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="9" t="s">
+      <c r="B18" s="6"/>
+      <c r="C18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="27"/>
-      <c r="L18" s="60"/>
-      <c r="M18" s="60"/>
-    </row>
-    <row r="19" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E18" s="22"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="28"/>
+      <c r="L18" s="61"/>
+      <c r="M18" s="61"/>
+    </row>
+    <row r="19" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A19" s="58"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="9" t="s">
+      <c r="B19" s="6"/>
+      <c r="C19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="27"/>
-    </row>
-    <row r="20" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E19" s="22"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="28"/>
+    </row>
+    <row r="20" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A20" s="58"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="9" t="s">
+      <c r="B20" s="6"/>
+      <c r="C20" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="27"/>
-    </row>
-    <row r="21" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E20" s="22"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="28"/>
+    </row>
+    <row r="21" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A21" s="58"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="9" t="s">
+      <c r="B21" s="6"/>
+      <c r="C21" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="27"/>
-    </row>
-    <row r="22" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E21" s="22"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="28"/>
+    </row>
+    <row r="22" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A22" s="58"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="9" t="s">
+      <c r="B22" s="6"/>
+      <c r="C22" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="27"/>
-      <c r="L22" s="57"/>
-      <c r="M22" s="57"/>
-    </row>
-    <row r="23" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E22" s="22"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="28"/>
+      <c r="L22" s="59"/>
+      <c r="M22" s="59"/>
+    </row>
+    <row r="23" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A23" s="58"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="9" t="s">
+      <c r="B23" s="6"/>
+      <c r="C23" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="27"/>
-      <c r="L23" s="57"/>
-      <c r="M23" s="57"/>
-    </row>
-    <row r="24" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E23" s="22"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="28"/>
+      <c r="L23" s="59"/>
+      <c r="M23" s="59"/>
+    </row>
+    <row r="24" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A24" s="58"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" s="9" t="s">
+      <c r="B24" s="6"/>
+      <c r="C24" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="27"/>
-    </row>
-    <row r="25" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E24" s="22"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="28"/>
+    </row>
+    <row r="25" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A25" s="58"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" s="9" t="s">
+      <c r="B25" s="6"/>
+      <c r="C25" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="27"/>
-    </row>
-    <row r="26" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E25" s="22"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="28"/>
+    </row>
+    <row r="26" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A26" s="58"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="9" t="s">
+      <c r="B26" s="6"/>
+      <c r="C26" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E26" s="7"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="27"/>
-      <c r="L26" s="57"/>
-      <c r="M26" s="57"/>
-    </row>
-    <row r="27" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E26" s="22"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="28"/>
+      <c r="L26" s="59"/>
+      <c r="M26" s="59"/>
+    </row>
+    <row r="27" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A27" s="58"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="9" t="s">
+      <c r="B27" s="6"/>
+      <c r="C27" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E27" s="7"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="27"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-    </row>
-    <row r="28" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E27" s="22"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="28"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+    </row>
+    <row r="28" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A28" s="58"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="9" t="s">
+      <c r="B28" s="6"/>
+      <c r="C28" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="27"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-    </row>
-    <row r="29" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E28" s="22"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="28"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+    </row>
+    <row r="29" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A29" s="58"/>
-      <c r="B29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="27"/>
-    </row>
-    <row r="30" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="B29" s="6"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="28"/>
+    </row>
+    <row r="30" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A30" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" s="9" t="s">
+      <c r="B30" s="6"/>
+      <c r="C30" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="27"/>
-    </row>
-    <row r="31" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E30" s="22"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="28"/>
+    </row>
+    <row r="31" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A31" s="58"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" s="9" t="s">
+      <c r="B31" s="6"/>
+      <c r="C31" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="27"/>
-    </row>
-    <row r="32" spans="1:13" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E31" s="22"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="28"/>
+    </row>
+    <row r="32" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A32" s="58"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="9" t="s">
+      <c r="B32" s="6"/>
+      <c r="C32" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E32" s="7"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="27"/>
-    </row>
-    <row r="33" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E32" s="22"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="28"/>
+    </row>
+    <row r="33" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A33" s="58"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="9" t="s">
+      <c r="B33" s="6"/>
+      <c r="C33" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="27"/>
-    </row>
-    <row r="34" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E33" s="22"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="28"/>
+    </row>
+    <row r="34" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A34" s="58"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="9" t="s">
+      <c r="B34" s="6"/>
+      <c r="C34" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="27"/>
-    </row>
-    <row r="35" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E34" s="22"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="28"/>
+    </row>
+    <row r="35" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A35" s="58"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="9" t="s">
+      <c r="B35" s="6"/>
+      <c r="C35" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E35" s="7"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="27"/>
-    </row>
-    <row r="36" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E35" s="22"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="28"/>
+    </row>
+    <row r="36" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A36" s="58"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D36" s="13" t="s">
+      <c r="B36" s="6"/>
+      <c r="C36" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E36" s="7"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="27"/>
-    </row>
-    <row r="37" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E36" s="22"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="28"/>
+    </row>
+    <row r="37" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A37" s="58"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D37" s="9" t="s">
+      <c r="B37" s="13"/>
+      <c r="C37" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E37" s="7"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="27"/>
-    </row>
-    <row r="38" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E37" s="22"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="28"/>
+    </row>
+    <row r="38" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A38" s="58"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D38" s="9" t="s">
+      <c r="B38" s="13"/>
+      <c r="C38" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E38" s="14"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="27"/>
-    </row>
-    <row r="39" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E38" s="25"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="28"/>
+    </row>
+    <row r="39" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A39" s="58"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D39" s="9" t="s">
+      <c r="B39" s="13"/>
+      <c r="C39" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E39" s="14"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="27"/>
-    </row>
-    <row r="40" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E39" s="25"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="28"/>
+    </row>
+    <row r="40" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A40" s="58"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D40" s="9" t="s">
+      <c r="B40" s="6"/>
+      <c r="C40" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E40" s="7"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="27"/>
-    </row>
-    <row r="41" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E40" s="22"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="28"/>
+    </row>
+    <row r="41" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A41" s="58"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D41" s="9" t="s">
+      <c r="B41" s="6"/>
+      <c r="C41" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E41" s="7"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="27"/>
-    </row>
-    <row r="42" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E41" s="22"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="28"/>
+    </row>
+    <row r="42" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A42" s="58"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D42" s="9" t="s">
+      <c r="B42" s="6"/>
+      <c r="C42" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E42" s="7"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="27"/>
-    </row>
-    <row r="43" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E42" s="22"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="28"/>
+    </row>
+    <row r="43" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A43" s="58"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" s="9" t="s">
+      <c r="B43" s="6"/>
+      <c r="C43" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E43" s="7"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="26"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="27"/>
-    </row>
-    <row r="44" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E43" s="22"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="28"/>
+    </row>
+    <row r="44" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A44" s="58"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D44" s="9" t="s">
+      <c r="B44" s="6"/>
+      <c r="C44" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E44" s="7"/>
-      <c r="F44" s="26"/>
-      <c r="G44" s="26"/>
-      <c r="H44" s="26"/>
-      <c r="I44" s="27"/>
-    </row>
-    <row r="45" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E44" s="22"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="27"/>
+      <c r="I44" s="28"/>
+    </row>
+    <row r="45" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A45" s="58"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D45" s="9" t="s">
+      <c r="B45" s="6"/>
+      <c r="C45" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E45" s="7"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="26"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="27"/>
-    </row>
-    <row r="46" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E45" s="22"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="27"/>
+      <c r="H45" s="27"/>
+      <c r="I45" s="28"/>
+    </row>
+    <row r="46" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A46" s="58"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D46" s="9" t="s">
+      <c r="B46" s="6"/>
+      <c r="C46" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E46" s="7"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="27"/>
-    </row>
-    <row r="47" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E46" s="22"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
+      <c r="I46" s="28"/>
+    </row>
+    <row r="47" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A47" s="58"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D47" s="9" t="s">
+      <c r="B47" s="6"/>
+      <c r="C47" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E47" s="7"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="27"/>
-    </row>
-    <row r="48" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E47" s="22"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="27"/>
+      <c r="I47" s="28"/>
+    </row>
+    <row r="48" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A48" s="58"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D48" s="9" t="s">
+      <c r="B48" s="6"/>
+      <c r="C48" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E48" s="7"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="26"/>
-      <c r="H48" s="26"/>
-      <c r="I48" s="27"/>
-    </row>
-    <row r="49" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E48" s="22"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27"/>
+      <c r="I48" s="28"/>
+    </row>
+    <row r="49" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A49" s="58"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D49" s="15" t="s">
+      <c r="B49" s="6"/>
+      <c r="C49" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="7"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
-      <c r="H49" s="26"/>
-      <c r="I49" s="27"/>
-    </row>
-    <row r="50" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E49" s="22"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="27"/>
+      <c r="I49" s="28"/>
+    </row>
+    <row r="50" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A50" s="58"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D50" s="17" t="s">
+      <c r="B50" s="6"/>
+      <c r="C50" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="E50" s="7"/>
-      <c r="F50" s="26"/>
-      <c r="G50" s="26"/>
-      <c r="H50" s="26"/>
-      <c r="I50" s="27"/>
-    </row>
-    <row r="51" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="E50" s="22"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="27"/>
+      <c r="I50" s="28"/>
+    </row>
+    <row r="51" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A51" s="58"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="26"/>
-      <c r="G51" s="26"/>
-      <c r="H51" s="26"/>
-      <c r="I51" s="27"/>
-    </row>
-    <row r="52" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="B51" s="6"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="27"/>
+      <c r="G51" s="27"/>
+      <c r="H51" s="27"/>
+      <c r="I51" s="28"/>
+    </row>
+    <row r="52" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
       <c r="A52" s="58"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="18"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="26"/>
-      <c r="G52" s="26"/>
-      <c r="H52" s="26"/>
-      <c r="I52" s="27"/>
-    </row>
-    <row r="53" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
-      <c r="A53" s="55" t="s">
+      <c r="B52" s="6"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="27"/>
+      <c r="I52" s="28"/>
+    </row>
+    <row r="53" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A53" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="B53" s="7"/>
-      <c r="C53" s="56" t="s">
+      <c r="B53" s="6"/>
+      <c r="C53" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="D53" s="56"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="26"/>
-      <c r="H53" s="26"/>
-      <c r="I53" s="27"/>
-    </row>
-    <row r="54" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
-      <c r="A54" s="55"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="56" t="s">
+      <c r="D53" s="57"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="27"/>
+      <c r="I53" s="28"/>
+    </row>
+    <row r="54" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A54" s="56"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="D54" s="56"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="26"/>
-      <c r="G54" s="26"/>
-      <c r="H54" s="26"/>
-      <c r="I54" s="27"/>
-    </row>
-    <row r="55" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
-      <c r="A55" s="55"/>
-      <c r="B55" s="7"/>
-      <c r="C55" s="56" t="s">
+      <c r="D54" s="57"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="27"/>
+      <c r="I54" s="28"/>
+    </row>
+    <row r="55" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A55" s="56"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="D55" s="56"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="26"/>
-      <c r="G55" s="26"/>
-      <c r="H55" s="26"/>
-      <c r="I55" s="27"/>
-    </row>
-    <row r="56" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
-      <c r="A56" s="55"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="56" t="s">
+      <c r="D55" s="57"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="27"/>
+      <c r="G55" s="27"/>
+      <c r="H55" s="27"/>
+      <c r="I55" s="28"/>
+    </row>
+    <row r="56" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A56" s="56"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="D56" s="56"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="26"/>
-      <c r="G56" s="26"/>
-      <c r="H56" s="26"/>
-      <c r="I56" s="27"/>
+      <c r="D56" s="57"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="27"/>
+      <c r="I56" s="28"/>
     </row>
     <row r="57" spans="1:9" ht="9" customHeight="1">
-      <c r="A57" s="47"/>
-      <c r="B57" s="20"/>
-      <c r="C57" s="49"/>
-      <c r="D57" s="50"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="51"/>
-      <c r="G57" s="51"/>
-      <c r="H57" s="51"/>
-      <c r="I57" s="52"/>
+      <c r="A57" s="48"/>
+      <c r="B57" s="19"/>
+      <c r="C57" s="50"/>
+      <c r="D57" s="51"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="52"/>
+      <c r="G57" s="52"/>
+      <c r="H57" s="52"/>
+      <c r="I57" s="53"/>
     </row>
     <row r="58" spans="1:9" ht="9" customHeight="1">
-      <c r="A58" s="47"/>
-      <c r="B58" s="20"/>
-      <c r="C58" s="49"/>
-      <c r="D58" s="50"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="53"/>
-      <c r="G58" s="53"/>
-      <c r="H58" s="53"/>
-      <c r="I58" s="54"/>
+      <c r="A58" s="48"/>
+      <c r="B58" s="19"/>
+      <c r="C58" s="50"/>
+      <c r="D58" s="51"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="54"/>
+      <c r="H58" s="54"/>
+      <c r="I58" s="55"/>
     </row>
     <row r="59" spans="1:9" ht="9" customHeight="1">
-      <c r="A59" s="47"/>
-      <c r="B59" s="20"/>
-      <c r="C59" s="49"/>
-      <c r="D59" s="50"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="32"/>
-      <c r="I59" s="33"/>
+      <c r="A59" s="48"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="50"/>
+      <c r="D59" s="51"/>
+      <c r="E59" s="23"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="33"/>
+      <c r="H59" s="33"/>
+      <c r="I59" s="34"/>
     </row>
     <row r="60" spans="1:9" ht="9" customHeight="1">
-      <c r="A60" s="47"/>
-      <c r="B60" s="20"/>
-      <c r="C60" s="49"/>
-      <c r="D60" s="50"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="32"/>
-      <c r="I60" s="33"/>
+      <c r="A60" s="48"/>
+      <c r="B60" s="19"/>
+      <c r="C60" s="50"/>
+      <c r="D60" s="51"/>
+      <c r="E60" s="23"/>
+      <c r="F60" s="33"/>
+      <c r="G60" s="33"/>
+      <c r="H60" s="33"/>
+      <c r="I60" s="34"/>
     </row>
     <row r="61" spans="1:9" ht="9" customHeight="1">
-      <c r="A61" s="48"/>
-      <c r="B61" s="20"/>
-      <c r="C61" s="49"/>
-      <c r="D61" s="50"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="32"/>
-      <c r="H61" s="32"/>
-      <c r="I61" s="33"/>
+      <c r="A61" s="49"/>
+      <c r="B61" s="19"/>
+      <c r="C61" s="50"/>
+      <c r="D61" s="51"/>
+      <c r="E61" s="23"/>
+      <c r="F61" s="33"/>
+      <c r="G61" s="33"/>
+      <c r="H61" s="33"/>
+      <c r="I61" s="34"/>
     </row>
     <row r="62" spans="1:9" ht="9" customHeight="1">
-      <c r="A62" s="34" t="s">
+      <c r="A62" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="35"/>
-      <c r="C62" s="35"/>
-      <c r="D62" s="36"/>
-      <c r="E62" s="43" t="s">
+      <c r="B62" s="36"/>
+      <c r="C62" s="36"/>
+      <c r="D62" s="37"/>
+      <c r="E62" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="F62" s="43"/>
-      <c r="G62" s="43"/>
-      <c r="H62" s="43"/>
-      <c r="I62" s="44"/>
+      <c r="F62" s="44"/>
+      <c r="G62" s="44"/>
+      <c r="H62" s="44"/>
+      <c r="I62" s="45"/>
     </row>
     <row r="63" spans="1:9" ht="9" customHeight="1">
-      <c r="A63" s="37"/>
-      <c r="B63" s="38"/>
-      <c r="C63" s="38"/>
-      <c r="D63" s="39"/>
-      <c r="E63" s="45" t="s">
+      <c r="A63" s="38"/>
+      <c r="B63" s="39"/>
+      <c r="C63" s="39"/>
+      <c r="D63" s="40"/>
+      <c r="E63" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="F63" s="45"/>
-      <c r="G63" s="45"/>
-      <c r="H63" s="45"/>
-      <c r="I63" s="5" t="s">
+      <c r="F63" s="46"/>
+      <c r="G63" s="46"/>
+      <c r="H63" s="46"/>
+      <c r="I63" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="9" customHeight="1">
-      <c r="A64" s="37"/>
-      <c r="B64" s="38"/>
-      <c r="C64" s="38"/>
-      <c r="D64" s="39"/>
-      <c r="E64" s="46"/>
-      <c r="F64" s="46"/>
-      <c r="G64" s="46"/>
-      <c r="H64" s="46"/>
-      <c r="I64" s="23"/>
+      <c r="A64" s="38"/>
+      <c r="B64" s="39"/>
+      <c r="C64" s="39"/>
+      <c r="D64" s="40"/>
+      <c r="E64" s="47"/>
+      <c r="F64" s="47"/>
+      <c r="G64" s="47"/>
+      <c r="H64" s="47"/>
+      <c r="I64" s="20"/>
     </row>
     <row r="65" spans="1:9" ht="9" customHeight="1">
-      <c r="A65" s="37"/>
-      <c r="B65" s="38"/>
-      <c r="C65" s="38"/>
-      <c r="D65" s="39"/>
-      <c r="E65" s="46"/>
-      <c r="F65" s="46"/>
-      <c r="G65" s="46"/>
-      <c r="H65" s="46"/>
-      <c r="I65" s="23"/>
+      <c r="A65" s="38"/>
+      <c r="B65" s="39"/>
+      <c r="C65" s="39"/>
+      <c r="D65" s="40"/>
+      <c r="E65" s="47"/>
+      <c r="F65" s="47"/>
+      <c r="G65" s="47"/>
+      <c r="H65" s="47"/>
+      <c r="I65" s="20"/>
     </row>
     <row r="66" spans="1:9" ht="9" customHeight="1">
-      <c r="A66" s="37"/>
-      <c r="B66" s="38"/>
-      <c r="C66" s="38"/>
-      <c r="D66" s="39"/>
-      <c r="E66" s="46"/>
-      <c r="F66" s="46"/>
-      <c r="G66" s="46"/>
-      <c r="H66" s="46"/>
-      <c r="I66" s="23"/>
+      <c r="A66" s="38"/>
+      <c r="B66" s="39"/>
+      <c r="C66" s="39"/>
+      <c r="D66" s="40"/>
+      <c r="E66" s="47"/>
+      <c r="F66" s="47"/>
+      <c r="G66" s="47"/>
+      <c r="H66" s="47"/>
+      <c r="I66" s="20"/>
     </row>
     <row r="67" spans="1:9" ht="9" customHeight="1">
-      <c r="A67" s="37"/>
-      <c r="B67" s="38"/>
-      <c r="C67" s="38"/>
-      <c r="D67" s="39"/>
-      <c r="E67" s="46"/>
-      <c r="F67" s="46"/>
-      <c r="G67" s="46"/>
-      <c r="H67" s="46"/>
-      <c r="I67" s="23"/>
+      <c r="A67" s="38"/>
+      <c r="B67" s="39"/>
+      <c r="C67" s="39"/>
+      <c r="D67" s="40"/>
+      <c r="E67" s="47"/>
+      <c r="F67" s="47"/>
+      <c r="G67" s="47"/>
+      <c r="H67" s="47"/>
+      <c r="I67" s="20"/>
     </row>
     <row r="68" spans="1:9" ht="9" customHeight="1">
-      <c r="A68" s="37"/>
-      <c r="B68" s="38"/>
-      <c r="C68" s="38"/>
-      <c r="D68" s="39"/>
-      <c r="E68" s="46"/>
-      <c r="F68" s="46"/>
-      <c r="G68" s="46"/>
-      <c r="H68" s="46"/>
-      <c r="I68" s="23"/>
+      <c r="A68" s="38"/>
+      <c r="B68" s="39"/>
+      <c r="C68" s="39"/>
+      <c r="D68" s="40"/>
+      <c r="E68" s="47"/>
+      <c r="F68" s="47"/>
+      <c r="G68" s="47"/>
+      <c r="H68" s="47"/>
+      <c r="I68" s="20"/>
     </row>
     <row r="69" spans="1:9" ht="9" customHeight="1">
-      <c r="A69" s="37"/>
-      <c r="B69" s="38"/>
-      <c r="C69" s="38"/>
-      <c r="D69" s="39"/>
-      <c r="E69" s="28" t="s">
+      <c r="A69" s="38"/>
+      <c r="B69" s="39"/>
+      <c r="C69" s="39"/>
+      <c r="D69" s="40"/>
+      <c r="E69" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="26"/>
-      <c r="I69" s="27"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="27"/>
+      <c r="I69" s="28"/>
     </row>
     <row r="70" spans="1:9" ht="9" customHeight="1">
-      <c r="A70" s="37"/>
-      <c r="B70" s="38"/>
-      <c r="C70" s="38"/>
-      <c r="D70" s="39"/>
-      <c r="E70" s="28" t="s">
+      <c r="A70" s="38"/>
+      <c r="B70" s="39"/>
+      <c r="C70" s="39"/>
+      <c r="D70" s="40"/>
+      <c r="E70" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28"/>
-      <c r="H70" s="26"/>
-      <c r="I70" s="27"/>
+      <c r="F70" s="29"/>
+      <c r="G70" s="29"/>
+      <c r="H70" s="27"/>
+      <c r="I70" s="28"/>
     </row>
     <row r="71" spans="1:9" ht="9" customHeight="1">
-      <c r="A71" s="37"/>
-      <c r="B71" s="38"/>
-      <c r="C71" s="38"/>
-      <c r="D71" s="39"/>
-      <c r="E71" s="28" t="s">
+      <c r="A71" s="38"/>
+      <c r="B71" s="39"/>
+      <c r="C71" s="39"/>
+      <c r="D71" s="40"/>
+      <c r="E71" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="F71" s="28"/>
-      <c r="G71" s="28"/>
-      <c r="H71" s="26"/>
-      <c r="I71" s="27"/>
+      <c r="F71" s="29"/>
+      <c r="G71" s="29"/>
+      <c r="H71" s="27"/>
+      <c r="I71" s="28"/>
     </row>
     <row r="72" spans="1:9" ht="9" customHeight="1">
-      <c r="A72" s="37"/>
-      <c r="B72" s="38"/>
-      <c r="C72" s="38"/>
-      <c r="D72" s="39"/>
-      <c r="E72" s="28" t="s">
+      <c r="A72" s="38"/>
+      <c r="B72" s="39"/>
+      <c r="C72" s="39"/>
+      <c r="D72" s="40"/>
+      <c r="E72" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="F72" s="28"/>
-      <c r="G72" s="28"/>
-      <c r="H72" s="26"/>
-      <c r="I72" s="27"/>
+      <c r="F72" s="29"/>
+      <c r="G72" s="29"/>
+      <c r="H72" s="27"/>
+      <c r="I72" s="28"/>
     </row>
     <row r="73" spans="1:9" ht="9" customHeight="1">
-      <c r="A73" s="37"/>
-      <c r="B73" s="38"/>
-      <c r="C73" s="38"/>
-      <c r="D73" s="39"/>
-      <c r="E73" s="28" t="s">
+      <c r="A73" s="38"/>
+      <c r="B73" s="39"/>
+      <c r="C73" s="39"/>
+      <c r="D73" s="40"/>
+      <c r="E73" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="F73" s="28"/>
-      <c r="G73" s="28"/>
-      <c r="H73" s="26"/>
-      <c r="I73" s="27"/>
+      <c r="F73" s="29"/>
+      <c r="G73" s="29"/>
+      <c r="H73" s="27"/>
+      <c r="I73" s="28"/>
     </row>
     <row r="74" spans="1:9" ht="9" customHeight="1" thickBot="1">
-      <c r="A74" s="40"/>
-      <c r="B74" s="41"/>
-      <c r="C74" s="41"/>
-      <c r="D74" s="42"/>
-      <c r="E74" s="31" t="s">
+      <c r="A74" s="41"/>
+      <c r="B74" s="42"/>
+      <c r="C74" s="42"/>
+      <c r="D74" s="43"/>
+      <c r="E74" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="F74" s="31"/>
-      <c r="G74" s="31"/>
-      <c r="H74" s="29"/>
-      <c r="I74" s="30"/>
+      <c r="F74" s="32"/>
+      <c r="G74" s="32"/>
+      <c r="H74" s="30"/>
+      <c r="I74" s="31"/>
     </row>
     <row r="75" spans="1:9" ht="9" customHeight="1" thickTop="1">
-      <c r="G75" s="25" t="s">
+      <c r="G75" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="H75" s="25"/>
-      <c r="I75" s="25"/>
+      <c r="H75" s="26"/>
+      <c r="I75" s="26"/>
     </row>
     <row r="76" spans="1:9" ht="9" customHeight="1">
       <c r="A76"/>
@@ -2407,7 +2410,6 @@
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="D2:I2"/>
-    <mergeCell ref="B3:C3"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="F10:I10"/>
@@ -2416,11 +2418,12 @@
     <mergeCell ref="F13:I13"/>
     <mergeCell ref="F14:I14"/>
     <mergeCell ref="F15:I15"/>
-    <mergeCell ref="B4:C4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="F5:I5"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
     <mergeCell ref="F22:I22"/>
     <mergeCell ref="L22:M22"/>
     <mergeCell ref="F23:I23"/>
@@ -2437,7 +2440,6 @@
     <mergeCell ref="F19:I19"/>
     <mergeCell ref="F20:I20"/>
     <mergeCell ref="F21:I21"/>
-    <mergeCell ref="F34:I34"/>
     <mergeCell ref="F35:I35"/>
     <mergeCell ref="F36:I36"/>
     <mergeCell ref="F37:I37"/>
@@ -2452,6 +2454,17 @@
     <mergeCell ref="F31:I31"/>
     <mergeCell ref="F32:I32"/>
     <mergeCell ref="F33:I33"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="A53:A56"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="A30:A52"/>
     <mergeCell ref="F46:I46"/>
     <mergeCell ref="F47:I47"/>
     <mergeCell ref="F48:I48"/>
@@ -2464,17 +2477,7 @@
     <mergeCell ref="F43:I43"/>
     <mergeCell ref="F44:I44"/>
     <mergeCell ref="F45:I45"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="A53:A56"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="A30:A52"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="F61:I61"/>
     <mergeCell ref="A62:D74"/>
     <mergeCell ref="E62:I62"/>

--- a/public/assets/templates/maintenance/electric_engine.xlsx
+++ b/public/assets/templates/maintenance/electric_engine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17AD7346-7B9E-4F64-B6A4-5D671C6F910A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C6ADB1-3B10-40FC-9AB3-0B29888F5D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{7A80608D-5162-4C69-AACA-06EF8CFA5F02}"/>
   </bookViews>
@@ -736,18 +736,129 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -757,143 +868,32 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1278,90 +1278,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" thickTop="1">
-      <c r="A1" s="63"/>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="67" t="s">
+      <c r="A1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="68"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="34"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="65"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="69" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="70"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="36"/>
     </row>
     <row r="3" spans="1:13" ht="10" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="71" t="s">
+      <c r="B3" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="72" t="s">
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="73"/>
-      <c r="G3" s="74" t="s">
+      <c r="F3" s="38"/>
+      <c r="G3" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="75"/>
-      <c r="I3" s="76"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="41"/>
     </row>
     <row r="4" spans="1:13" ht="10" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="72" t="s">
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="73"/>
-      <c r="G4" s="74" t="s">
+      <c r="F4" s="38"/>
+      <c r="G4" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="75"/>
-      <c r="I4" s="76"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="41"/>
     </row>
     <row r="5" spans="1:13" s="5" customFormat="1" ht="11" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
       <c r="E5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="46" t="s">
+      <c r="F5" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="78"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="44"/>
     </row>
     <row r="6" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A6" s="62" t="s">
+      <c r="A6" s="26" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="6"/>
@@ -1378,7 +1378,7 @@
       <c r="I6" s="28"/>
     </row>
     <row r="7" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A7" s="62"/>
+      <c r="A7" s="26"/>
       <c r="B7" s="6"/>
       <c r="C7" s="7" t="s">
         <v>12</v>
@@ -1393,7 +1393,7 @@
       <c r="I7" s="28"/>
     </row>
     <row r="8" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A8" s="62"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7" t="s">
         <v>12</v>
@@ -1408,7 +1408,7 @@
       <c r="I8" s="28"/>
     </row>
     <row r="9" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A9" s="62"/>
+      <c r="A9" s="26"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7" t="s">
         <v>12</v>
@@ -1423,7 +1423,7 @@
       <c r="I9" s="28"/>
     </row>
     <row r="10" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A10" s="62"/>
+      <c r="A10" s="26"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
         <v>12</v>
@@ -1438,7 +1438,7 @@
       <c r="I10" s="28"/>
     </row>
     <row r="11" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A11" s="62"/>
+      <c r="A11" s="26"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7" t="s">
         <v>12</v>
@@ -1453,7 +1453,7 @@
       <c r="I11" s="28"/>
     </row>
     <row r="12" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A12" s="62"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7" t="s">
         <v>12</v>
@@ -1468,7 +1468,7 @@
       <c r="I12" s="28"/>
     </row>
     <row r="13" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A13" s="62"/>
+      <c r="A13" s="26"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7" t="s">
         <v>12</v>
@@ -1483,7 +1483,7 @@
       <c r="I13" s="28"/>
     </row>
     <row r="14" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A14" s="62"/>
+      <c r="A14" s="26"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
       <c r="D14" s="8"/>
@@ -1494,7 +1494,7 @@
       <c r="I14" s="28"/>
     </row>
     <row r="15" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A15" s="62"/>
+      <c r="A15" s="26"/>
       <c r="B15" s="6"/>
       <c r="E15" s="22"/>
       <c r="F15" s="27"/>
@@ -1503,7 +1503,7 @@
       <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A16" s="58" t="s">
+      <c r="A16" s="47" t="s">
         <v>21</v>
       </c>
       <c r="B16" s="6"/>
@@ -1518,11 +1518,11 @@
       <c r="G16" s="27"/>
       <c r="H16" s="27"/>
       <c r="I16" s="28"/>
-      <c r="L16" s="60"/>
-      <c r="M16" s="60"/>
+      <c r="L16" s="48"/>
+      <c r="M16" s="48"/>
     </row>
     <row r="17" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A17" s="58"/>
+      <c r="A17" s="47"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7" t="s">
         <v>12</v>
@@ -1535,11 +1535,11 @@
       <c r="G17" s="27"/>
       <c r="H17" s="27"/>
       <c r="I17" s="28"/>
-      <c r="L17" s="61"/>
-      <c r="M17" s="61"/>
+      <c r="L17" s="49"/>
+      <c r="M17" s="49"/>
     </row>
     <row r="18" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A18" s="58"/>
+      <c r="A18" s="47"/>
       <c r="B18" s="6"/>
       <c r="C18" s="7" t="s">
         <v>12</v>
@@ -1552,11 +1552,11 @@
       <c r="G18" s="27"/>
       <c r="H18" s="27"/>
       <c r="I18" s="28"/>
-      <c r="L18" s="61"/>
-      <c r="M18" s="61"/>
+      <c r="L18" s="49"/>
+      <c r="M18" s="49"/>
     </row>
     <row r="19" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A19" s="58"/>
+      <c r="A19" s="47"/>
       <c r="B19" s="6"/>
       <c r="C19" s="7" t="s">
         <v>12</v>
@@ -1571,7 +1571,7 @@
       <c r="I19" s="28"/>
     </row>
     <row r="20" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A20" s="58"/>
+      <c r="A20" s="47"/>
       <c r="B20" s="6"/>
       <c r="C20" s="7" t="s">
         <v>12</v>
@@ -1586,7 +1586,7 @@
       <c r="I20" s="28"/>
     </row>
     <row r="21" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A21" s="58"/>
+      <c r="A21" s="47"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7" t="s">
         <v>12</v>
@@ -1601,7 +1601,7 @@
       <c r="I21" s="28"/>
     </row>
     <row r="22" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A22" s="58"/>
+      <c r="A22" s="47"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7" t="s">
         <v>12</v>
@@ -1614,11 +1614,11 @@
       <c r="G22" s="27"/>
       <c r="H22" s="27"/>
       <c r="I22" s="28"/>
-      <c r="L22" s="59"/>
-      <c r="M22" s="59"/>
+      <c r="L22" s="46"/>
+      <c r="M22" s="46"/>
     </row>
     <row r="23" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A23" s="58"/>
+      <c r="A23" s="47"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7" t="s">
         <v>12</v>
@@ -1631,11 +1631,11 @@
       <c r="G23" s="27"/>
       <c r="H23" s="27"/>
       <c r="I23" s="28"/>
-      <c r="L23" s="59"/>
-      <c r="M23" s="59"/>
+      <c r="L23" s="46"/>
+      <c r="M23" s="46"/>
     </row>
     <row r="24" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A24" s="58"/>
+      <c r="A24" s="47"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7" t="s">
         <v>12</v>
@@ -1650,7 +1650,7 @@
       <c r="I24" s="28"/>
     </row>
     <row r="25" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A25" s="58"/>
+      <c r="A25" s="47"/>
       <c r="B25" s="6"/>
       <c r="C25" s="7" t="s">
         <v>12</v>
@@ -1665,7 +1665,7 @@
       <c r="I25" s="28"/>
     </row>
     <row r="26" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A26" s="58"/>
+      <c r="A26" s="47"/>
       <c r="B26" s="6"/>
       <c r="C26" s="7" t="s">
         <v>12</v>
@@ -1678,11 +1678,11 @@
       <c r="G26" s="27"/>
       <c r="H26" s="27"/>
       <c r="I26" s="28"/>
-      <c r="L26" s="59"/>
-      <c r="M26" s="59"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
     </row>
     <row r="27" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A27" s="58"/>
+      <c r="A27" s="47"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7" t="s">
         <v>12</v>
@@ -1699,7 +1699,7 @@
       <c r="M27" s="11"/>
     </row>
     <row r="28" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A28" s="58"/>
+      <c r="A28" s="47"/>
       <c r="B28" s="6"/>
       <c r="C28" s="7" t="s">
         <v>12</v>
@@ -1716,7 +1716,7 @@
       <c r="M28" s="11"/>
     </row>
     <row r="29" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A29" s="58"/>
+      <c r="A29" s="47"/>
       <c r="B29" s="6"/>
       <c r="E29" s="22"/>
       <c r="F29" s="27"/>
@@ -1725,7 +1725,7 @@
       <c r="I29" s="28"/>
     </row>
     <row r="30" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A30" s="58" t="s">
+      <c r="A30" s="47" t="s">
         <v>35</v>
       </c>
       <c r="B30" s="6"/>
@@ -1742,7 +1742,7 @@
       <c r="I30" s="28"/>
     </row>
     <row r="31" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A31" s="58"/>
+      <c r="A31" s="47"/>
       <c r="B31" s="6"/>
       <c r="C31" s="7" t="s">
         <v>12</v>
@@ -1757,7 +1757,7 @@
       <c r="I31" s="28"/>
     </row>
     <row r="32" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A32" s="58"/>
+      <c r="A32" s="47"/>
       <c r="B32" s="6"/>
       <c r="C32" s="7" t="s">
         <v>12</v>
@@ -1772,7 +1772,7 @@
       <c r="I32" s="28"/>
     </row>
     <row r="33" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A33" s="58"/>
+      <c r="A33" s="47"/>
       <c r="B33" s="6"/>
       <c r="C33" s="7" t="s">
         <v>12</v>
@@ -1787,7 +1787,7 @@
       <c r="I33" s="28"/>
     </row>
     <row r="34" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A34" s="58"/>
+      <c r="A34" s="47"/>
       <c r="B34" s="6"/>
       <c r="C34" s="7" t="s">
         <v>12</v>
@@ -1802,7 +1802,7 @@
       <c r="I34" s="28"/>
     </row>
     <row r="35" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A35" s="58"/>
+      <c r="A35" s="47"/>
       <c r="B35" s="6"/>
       <c r="C35" s="7" t="s">
         <v>12</v>
@@ -1817,7 +1817,7 @@
       <c r="I35" s="28"/>
     </row>
     <row r="36" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A36" s="58"/>
+      <c r="A36" s="47"/>
       <c r="B36" s="6"/>
       <c r="C36" s="7" t="s">
         <v>12</v>
@@ -1832,7 +1832,7 @@
       <c r="I36" s="28"/>
     </row>
     <row r="37" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A37" s="58"/>
+      <c r="A37" s="47"/>
       <c r="B37" s="13"/>
       <c r="C37" s="7" t="s">
         <v>12</v>
@@ -1847,7 +1847,7 @@
       <c r="I37" s="28"/>
     </row>
     <row r="38" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A38" s="58"/>
+      <c r="A38" s="47"/>
       <c r="B38" s="13"/>
       <c r="C38" s="7" t="s">
         <v>12</v>
@@ -1862,7 +1862,7 @@
       <c r="I38" s="28"/>
     </row>
     <row r="39" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A39" s="58"/>
+      <c r="A39" s="47"/>
       <c r="B39" s="13"/>
       <c r="C39" s="7" t="s">
         <v>12</v>
@@ -1877,7 +1877,7 @@
       <c r="I39" s="28"/>
     </row>
     <row r="40" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A40" s="58"/>
+      <c r="A40" s="47"/>
       <c r="B40" s="6"/>
       <c r="C40" s="7" t="s">
         <v>12</v>
@@ -1892,7 +1892,7 @@
       <c r="I40" s="28"/>
     </row>
     <row r="41" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A41" s="58"/>
+      <c r="A41" s="47"/>
       <c r="B41" s="6"/>
       <c r="C41" s="7" t="s">
         <v>12</v>
@@ -1907,7 +1907,7 @@
       <c r="I41" s="28"/>
     </row>
     <row r="42" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A42" s="58"/>
+      <c r="A42" s="47"/>
       <c r="B42" s="6"/>
       <c r="C42" s="7" t="s">
         <v>12</v>
@@ -1922,7 +1922,7 @@
       <c r="I42" s="28"/>
     </row>
     <row r="43" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A43" s="58"/>
+      <c r="A43" s="47"/>
       <c r="B43" s="6"/>
       <c r="C43" s="7" t="s">
         <v>12</v>
@@ -1937,7 +1937,7 @@
       <c r="I43" s="28"/>
     </row>
     <row r="44" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A44" s="58"/>
+      <c r="A44" s="47"/>
       <c r="B44" s="6"/>
       <c r="C44" s="7" t="s">
         <v>12</v>
@@ -1952,7 +1952,7 @@
       <c r="I44" s="28"/>
     </row>
     <row r="45" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A45" s="58"/>
+      <c r="A45" s="47"/>
       <c r="B45" s="6"/>
       <c r="C45" s="7" t="s">
         <v>12</v>
@@ -1967,7 +1967,7 @@
       <c r="I45" s="28"/>
     </row>
     <row r="46" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A46" s="58"/>
+      <c r="A46" s="47"/>
       <c r="B46" s="6"/>
       <c r="C46" s="7" t="s">
         <v>12</v>
@@ -1982,7 +1982,7 @@
       <c r="I46" s="28"/>
     </row>
     <row r="47" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A47" s="58"/>
+      <c r="A47" s="47"/>
       <c r="B47" s="6"/>
       <c r="C47" s="7" t="s">
         <v>12</v>
@@ -1997,7 +1997,7 @@
       <c r="I47" s="28"/>
     </row>
     <row r="48" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A48" s="58"/>
+      <c r="A48" s="47"/>
       <c r="B48" s="6"/>
       <c r="C48" s="7" t="s">
         <v>12</v>
@@ -2012,7 +2012,7 @@
       <c r="I48" s="28"/>
     </row>
     <row r="49" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A49" s="58"/>
+      <c r="A49" s="47"/>
       <c r="B49" s="6"/>
       <c r="C49" s="7" t="s">
         <v>12</v>
@@ -2027,7 +2027,7 @@
       <c r="I49" s="28"/>
     </row>
     <row r="50" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A50" s="58"/>
+      <c r="A50" s="47"/>
       <c r="B50" s="6"/>
       <c r="C50" s="15" t="s">
         <v>12</v>
@@ -2042,7 +2042,7 @@
       <c r="I50" s="28"/>
     </row>
     <row r="51" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A51" s="58"/>
+      <c r="A51" s="47"/>
       <c r="B51" s="6"/>
       <c r="C51" s="7"/>
       <c r="D51" s="14"/>
@@ -2053,7 +2053,7 @@
       <c r="I51" s="28"/>
     </row>
     <row r="52" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A52" s="58"/>
+      <c r="A52" s="47"/>
       <c r="B52" s="6"/>
       <c r="C52" s="17"/>
       <c r="D52" s="18"/>
@@ -2064,14 +2064,14 @@
       <c r="I52" s="28"/>
     </row>
     <row r="53" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A53" s="56" t="s">
+      <c r="A53" s="50" t="s">
         <v>57</v>
       </c>
       <c r="B53" s="6"/>
-      <c r="C53" s="57" t="s">
+      <c r="C53" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="D53" s="57"/>
+      <c r="D53" s="51"/>
       <c r="E53" s="22"/>
       <c r="F53" s="27"/>
       <c r="G53" s="27"/>
@@ -2079,12 +2079,12 @@
       <c r="I53" s="28"/>
     </row>
     <row r="54" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A54" s="56"/>
+      <c r="A54" s="50"/>
       <c r="B54" s="6"/>
-      <c r="C54" s="57" t="s">
+      <c r="C54" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="D54" s="57"/>
+      <c r="D54" s="51"/>
       <c r="E54" s="22"/>
       <c r="F54" s="27"/>
       <c r="G54" s="27"/>
@@ -2092,12 +2092,12 @@
       <c r="I54" s="28"/>
     </row>
     <row r="55" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A55" s="56"/>
+      <c r="A55" s="50"/>
       <c r="B55" s="6"/>
-      <c r="C55" s="57" t="s">
+      <c r="C55" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="D55" s="57"/>
+      <c r="D55" s="51"/>
       <c r="E55" s="22"/>
       <c r="F55" s="27"/>
       <c r="G55" s="27"/>
@@ -2105,12 +2105,12 @@
       <c r="I55" s="28"/>
     </row>
     <row r="56" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A56" s="56"/>
+      <c r="A56" s="50"/>
       <c r="B56" s="13"/>
-      <c r="C56" s="57" t="s">
+      <c r="C56" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="D56" s="57"/>
+      <c r="D56" s="51"/>
       <c r="E56" s="25"/>
       <c r="F56" s="27"/>
       <c r="G56" s="27"/>
@@ -2118,229 +2118,229 @@
       <c r="I56" s="28"/>
     </row>
     <row r="57" spans="1:9" ht="9" customHeight="1">
-      <c r="A57" s="48"/>
+      <c r="A57" s="58"/>
       <c r="B57" s="19"/>
-      <c r="C57" s="50"/>
-      <c r="D57" s="51"/>
+      <c r="C57" s="60"/>
+      <c r="D57" s="61"/>
       <c r="E57" s="24"/>
-      <c r="F57" s="52"/>
-      <c r="G57" s="52"/>
-      <c r="H57" s="52"/>
-      <c r="I57" s="53"/>
+      <c r="F57" s="62"/>
+      <c r="G57" s="62"/>
+      <c r="H57" s="62"/>
+      <c r="I57" s="63"/>
     </row>
     <row r="58" spans="1:9" ht="9" customHeight="1">
-      <c r="A58" s="48"/>
+      <c r="A58" s="58"/>
       <c r="B58" s="19"/>
-      <c r="C58" s="50"/>
-      <c r="D58" s="51"/>
+      <c r="C58" s="60"/>
+      <c r="D58" s="61"/>
       <c r="E58" s="24"/>
-      <c r="F58" s="54"/>
-      <c r="G58" s="54"/>
-      <c r="H58" s="54"/>
-      <c r="I58" s="55"/>
+      <c r="F58" s="64"/>
+      <c r="G58" s="64"/>
+      <c r="H58" s="64"/>
+      <c r="I58" s="65"/>
     </row>
     <row r="59" spans="1:9" ht="9" customHeight="1">
-      <c r="A59" s="48"/>
+      <c r="A59" s="58"/>
       <c r="B59" s="19"/>
-      <c r="C59" s="50"/>
-      <c r="D59" s="51"/>
+      <c r="C59" s="60"/>
+      <c r="D59" s="61"/>
       <c r="E59" s="23"/>
-      <c r="F59" s="33"/>
-      <c r="G59" s="33"/>
-      <c r="H59" s="33"/>
-      <c r="I59" s="34"/>
+      <c r="F59" s="52"/>
+      <c r="G59" s="52"/>
+      <c r="H59" s="52"/>
+      <c r="I59" s="53"/>
     </row>
     <row r="60" spans="1:9" ht="9" customHeight="1">
-      <c r="A60" s="48"/>
+      <c r="A60" s="58"/>
       <c r="B60" s="19"/>
-      <c r="C60" s="50"/>
-      <c r="D60" s="51"/>
+      <c r="C60" s="60"/>
+      <c r="D60" s="61"/>
       <c r="E60" s="23"/>
-      <c r="F60" s="33"/>
-      <c r="G60" s="33"/>
-      <c r="H60" s="33"/>
-      <c r="I60" s="34"/>
+      <c r="F60" s="52"/>
+      <c r="G60" s="52"/>
+      <c r="H60" s="52"/>
+      <c r="I60" s="53"/>
     </row>
     <row r="61" spans="1:9" ht="9" customHeight="1">
-      <c r="A61" s="49"/>
+      <c r="A61" s="59"/>
       <c r="B61" s="19"/>
-      <c r="C61" s="50"/>
-      <c r="D61" s="51"/>
+      <c r="C61" s="60"/>
+      <c r="D61" s="61"/>
       <c r="E61" s="23"/>
-      <c r="F61" s="33"/>
-      <c r="G61" s="33"/>
-      <c r="H61" s="33"/>
-      <c r="I61" s="34"/>
+      <c r="F61" s="52"/>
+      <c r="G61" s="52"/>
+      <c r="H61" s="52"/>
+      <c r="I61" s="53"/>
     </row>
     <row r="62" spans="1:9" ht="9" customHeight="1">
-      <c r="A62" s="35" t="s">
+      <c r="A62" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="36"/>
-      <c r="C62" s="36"/>
-      <c r="D62" s="37"/>
-      <c r="E62" s="44" t="s">
+      <c r="B62" s="71"/>
+      <c r="C62" s="71"/>
+      <c r="D62" s="72"/>
+      <c r="E62" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="F62" s="44"/>
-      <c r="G62" s="44"/>
-      <c r="H62" s="44"/>
-      <c r="I62" s="45"/>
+      <c r="F62" s="54"/>
+      <c r="G62" s="54"/>
+      <c r="H62" s="54"/>
+      <c r="I62" s="55"/>
     </row>
     <row r="63" spans="1:9" ht="9" customHeight="1">
-      <c r="A63" s="38"/>
-      <c r="B63" s="39"/>
-      <c r="C63" s="39"/>
-      <c r="D63" s="40"/>
-      <c r="E63" s="46" t="s">
+      <c r="A63" s="73"/>
+      <c r="B63" s="74"/>
+      <c r="C63" s="74"/>
+      <c r="D63" s="75"/>
+      <c r="E63" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="F63" s="46"/>
-      <c r="G63" s="46"/>
-      <c r="H63" s="46"/>
+      <c r="F63" s="43"/>
+      <c r="G63" s="43"/>
+      <c r="H63" s="43"/>
       <c r="I63" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="9" customHeight="1">
-      <c r="A64" s="38"/>
-      <c r="B64" s="39"/>
-      <c r="C64" s="39"/>
-      <c r="D64" s="40"/>
-      <c r="E64" s="47"/>
-      <c r="F64" s="47"/>
-      <c r="G64" s="47"/>
-      <c r="H64" s="47"/>
+      <c r="A64" s="73"/>
+      <c r="B64" s="74"/>
+      <c r="C64" s="74"/>
+      <c r="D64" s="75"/>
+      <c r="E64" s="56"/>
+      <c r="F64" s="56"/>
+      <c r="G64" s="56"/>
+      <c r="H64" s="56"/>
       <c r="I64" s="20"/>
     </row>
     <row r="65" spans="1:9" ht="9" customHeight="1">
-      <c r="A65" s="38"/>
-      <c r="B65" s="39"/>
-      <c r="C65" s="39"/>
-      <c r="D65" s="40"/>
-      <c r="E65" s="47"/>
-      <c r="F65" s="47"/>
-      <c r="G65" s="47"/>
-      <c r="H65" s="47"/>
+      <c r="A65" s="73"/>
+      <c r="B65" s="74"/>
+      <c r="C65" s="74"/>
+      <c r="D65" s="75"/>
+      <c r="E65" s="56"/>
+      <c r="F65" s="56"/>
+      <c r="G65" s="56"/>
+      <c r="H65" s="56"/>
       <c r="I65" s="20"/>
     </row>
     <row r="66" spans="1:9" ht="9" customHeight="1">
-      <c r="A66" s="38"/>
-      <c r="B66" s="39"/>
-      <c r="C66" s="39"/>
-      <c r="D66" s="40"/>
-      <c r="E66" s="47"/>
-      <c r="F66" s="47"/>
-      <c r="G66" s="47"/>
-      <c r="H66" s="47"/>
+      <c r="A66" s="73"/>
+      <c r="B66" s="74"/>
+      <c r="C66" s="74"/>
+      <c r="D66" s="75"/>
+      <c r="E66" s="56"/>
+      <c r="F66" s="56"/>
+      <c r="G66" s="56"/>
+      <c r="H66" s="56"/>
       <c r="I66" s="20"/>
     </row>
     <row r="67" spans="1:9" ht="9" customHeight="1">
-      <c r="A67" s="38"/>
-      <c r="B67" s="39"/>
-      <c r="C67" s="39"/>
-      <c r="D67" s="40"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="47"/>
-      <c r="G67" s="47"/>
-      <c r="H67" s="47"/>
+      <c r="A67" s="73"/>
+      <c r="B67" s="74"/>
+      <c r="C67" s="74"/>
+      <c r="D67" s="75"/>
+      <c r="E67" s="56"/>
+      <c r="F67" s="56"/>
+      <c r="G67" s="56"/>
+      <c r="H67" s="56"/>
       <c r="I67" s="20"/>
     </row>
     <row r="68" spans="1:9" ht="9" customHeight="1">
-      <c r="A68" s="38"/>
-      <c r="B68" s="39"/>
-      <c r="C68" s="39"/>
-      <c r="D68" s="40"/>
-      <c r="E68" s="47"/>
-      <c r="F68" s="47"/>
-      <c r="G68" s="47"/>
-      <c r="H68" s="47"/>
+      <c r="A68" s="73"/>
+      <c r="B68" s="74"/>
+      <c r="C68" s="74"/>
+      <c r="D68" s="75"/>
+      <c r="E68" s="56"/>
+      <c r="F68" s="56"/>
+      <c r="G68" s="56"/>
+      <c r="H68" s="56"/>
       <c r="I68" s="20"/>
     </row>
     <row r="69" spans="1:9" ht="9" customHeight="1">
-      <c r="A69" s="38"/>
-      <c r="B69" s="39"/>
-      <c r="C69" s="39"/>
-      <c r="D69" s="40"/>
-      <c r="E69" s="29" t="s">
+      <c r="A69" s="73"/>
+      <c r="B69" s="74"/>
+      <c r="C69" s="74"/>
+      <c r="D69" s="75"/>
+      <c r="E69" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29"/>
+      <c r="F69" s="57"/>
+      <c r="G69" s="57"/>
       <c r="H69" s="27"/>
       <c r="I69" s="28"/>
     </row>
     <row r="70" spans="1:9" ht="9" customHeight="1">
-      <c r="A70" s="38"/>
-      <c r="B70" s="39"/>
-      <c r="C70" s="39"/>
-      <c r="D70" s="40"/>
-      <c r="E70" s="29" t="s">
+      <c r="A70" s="73"/>
+      <c r="B70" s="74"/>
+      <c r="C70" s="74"/>
+      <c r="D70" s="75"/>
+      <c r="E70" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
+      <c r="F70" s="57"/>
+      <c r="G70" s="57"/>
       <c r="H70" s="27"/>
       <c r="I70" s="28"/>
     </row>
     <row r="71" spans="1:9" ht="9" customHeight="1">
-      <c r="A71" s="38"/>
-      <c r="B71" s="39"/>
-      <c r="C71" s="39"/>
-      <c r="D71" s="40"/>
-      <c r="E71" s="29" t="s">
+      <c r="A71" s="73"/>
+      <c r="B71" s="74"/>
+      <c r="C71" s="74"/>
+      <c r="D71" s="75"/>
+      <c r="E71" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="F71" s="29"/>
-      <c r="G71" s="29"/>
+      <c r="F71" s="57"/>
+      <c r="G71" s="57"/>
       <c r="H71" s="27"/>
       <c r="I71" s="28"/>
     </row>
     <row r="72" spans="1:9" ht="9" customHeight="1">
-      <c r="A72" s="38"/>
-      <c r="B72" s="39"/>
-      <c r="C72" s="39"/>
-      <c r="D72" s="40"/>
-      <c r="E72" s="29" t="s">
+      <c r="A72" s="73"/>
+      <c r="B72" s="74"/>
+      <c r="C72" s="74"/>
+      <c r="D72" s="75"/>
+      <c r="E72" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="F72" s="29"/>
-      <c r="G72" s="29"/>
+      <c r="F72" s="57"/>
+      <c r="G72" s="57"/>
       <c r="H72" s="27"/>
       <c r="I72" s="28"/>
     </row>
     <row r="73" spans="1:9" ht="9" customHeight="1">
-      <c r="A73" s="38"/>
-      <c r="B73" s="39"/>
-      <c r="C73" s="39"/>
-      <c r="D73" s="40"/>
-      <c r="E73" s="29" t="s">
+      <c r="A73" s="73"/>
+      <c r="B73" s="74"/>
+      <c r="C73" s="74"/>
+      <c r="D73" s="75"/>
+      <c r="E73" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="F73" s="29"/>
-      <c r="G73" s="29"/>
+      <c r="F73" s="57"/>
+      <c r="G73" s="57"/>
       <c r="H73" s="27"/>
       <c r="I73" s="28"/>
     </row>
     <row r="74" spans="1:9" ht="9" customHeight="1" thickBot="1">
-      <c r="A74" s="41"/>
-      <c r="B74" s="42"/>
-      <c r="C74" s="42"/>
-      <c r="D74" s="43"/>
-      <c r="E74" s="32" t="s">
+      <c r="A74" s="76"/>
+      <c r="B74" s="77"/>
+      <c r="C74" s="77"/>
+      <c r="D74" s="78"/>
+      <c r="E74" s="69" t="s">
         <v>71</v>
       </c>
-      <c r="F74" s="32"/>
-      <c r="G74" s="32"/>
-      <c r="H74" s="30"/>
-      <c r="I74" s="31"/>
+      <c r="F74" s="69"/>
+      <c r="G74" s="69"/>
+      <c r="H74" s="67"/>
+      <c r="I74" s="68"/>
     </row>
     <row r="75" spans="1:9" ht="9" customHeight="1" thickTop="1">
-      <c r="G75" s="26" t="s">
+      <c r="G75" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="H75" s="26"/>
-      <c r="I75" s="26"/>
+      <c r="H75" s="66"/>
+      <c r="I75" s="66"/>
     </row>
     <row r="76" spans="1:9" ht="9" customHeight="1">
       <c r="A76"/>
@@ -2402,58 +2402,35 @@
     <row r="83" customFormat="1"/>
   </sheetData>
   <mergeCells count="105">
-    <mergeCell ref="A6:A15"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="A16:A29"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="F28:I28"/>
-    <mergeCell ref="F29:I29"/>
-    <mergeCell ref="F30:I30"/>
-    <mergeCell ref="F31:I31"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="G75:I75"/>
+    <mergeCell ref="H69:I70"/>
+    <mergeCell ref="E70:G70"/>
+    <mergeCell ref="E71:G71"/>
+    <mergeCell ref="H71:I72"/>
+    <mergeCell ref="E72:G72"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="H73:I74"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="F61:I61"/>
+    <mergeCell ref="A62:D74"/>
+    <mergeCell ref="E62:I62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="A57:A61"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="C61:D61"/>
     <mergeCell ref="F52:I52"/>
     <mergeCell ref="A53:A56"/>
     <mergeCell ref="C53:D53"/>
@@ -2478,35 +2455,58 @@
     <mergeCell ref="F44:I44"/>
     <mergeCell ref="F45:I45"/>
     <mergeCell ref="F34:I34"/>
-    <mergeCell ref="F61:I61"/>
-    <mergeCell ref="A62:D74"/>
-    <mergeCell ref="E62:I62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:G69"/>
-    <mergeCell ref="A57:A61"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="F59:I59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="G75:I75"/>
-    <mergeCell ref="H69:I70"/>
-    <mergeCell ref="E70:G70"/>
-    <mergeCell ref="E71:G71"/>
-    <mergeCell ref="H71:I72"/>
-    <mergeCell ref="E72:G72"/>
-    <mergeCell ref="E73:G73"/>
-    <mergeCell ref="H73:I74"/>
-    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="F30:I30"/>
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="A16:A29"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="A6:A15"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.43263888888888902" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/maintenance/electric_engine.xlsx
+++ b/public/assets/templates/maintenance/electric_engine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C6ADB1-3B10-40FC-9AB3-0B29888F5D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC6B1D4-6BBE-4CD9-A85F-D187281B8196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{7A80608D-5162-4C69-AACA-06EF8CFA5F02}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="ELECTRIC ENGINE" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'ELECTRIC ENGINE'!$A$1:$I$75</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'ELECTRIC ENGINE'!$A$1:$I$78</definedName>
   </definedNames>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="79">
   <si>
     <t>LAPORAN MAINTENANCE ELECTRIC ENGINE</t>
   </si>
@@ -42,15 +42,9 @@
     <t>Nama Mesin</t>
   </si>
   <si>
-    <t xml:space="preserve">Waktu   </t>
-  </si>
-  <si>
     <t>Running Hour</t>
   </si>
   <si>
-    <t xml:space="preserve">:  </t>
-  </si>
-  <si>
     <t>Mesin</t>
   </si>
   <si>
@@ -250,6 +244,27 @@
   </si>
   <si>
     <t xml:space="preserve">Tanggal </t>
+  </si>
+  <si>
+    <t>Waktu Mulai</t>
+  </si>
+  <si>
+    <t>Waktu Selesai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">: </t>
+  </si>
+  <si>
+    <t>Kode Mesin</t>
+  </si>
+  <si>
+    <t>Lokasi</t>
+  </si>
+  <si>
+    <t>Paket</t>
+  </si>
+  <si>
+    <t>Departemen</t>
   </si>
 </sst>
 </file>
@@ -657,7 +672,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -736,6 +751,21 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -793,9 +823,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -820,6 +847,33 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -868,32 +922,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1262,7 +1292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC5D322C-4578-4471-B9FD-0A0DA5343548}">
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11" style="21" customWidth="1"/>
@@ -1277,1105 +1307,1125 @@
     <col min="13" max="13" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" thickTop="1">
-      <c r="A1" s="29"/>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="33" t="s">
+    <row r="1" spans="1:9" ht="15" thickTop="1">
+      <c r="A1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="31"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="35" t="s">
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="39"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="36"/>
-    </row>
-    <row r="3" spans="1:13" ht="10" customHeight="1">
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="41"/>
+    </row>
+    <row r="3" spans="1:9" ht="10" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="43"/>
+      <c r="G3" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="30"/>
+    </row>
+    <row r="4" spans="1:9" ht="10" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" s="29"/>
+      <c r="I4" s="30"/>
+    </row>
+    <row r="5" spans="1:9" ht="10" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B5" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5" s="29"/>
+      <c r="I5" s="30"/>
+    </row>
+    <row r="6" spans="1:9" ht="10" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="38"/>
-      <c r="G3" s="39" t="s">
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="43"/>
+      <c r="G6" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" s="29"/>
+      <c r="I6" s="30"/>
+    </row>
+    <row r="7" spans="1:9" ht="10" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="40"/>
-      <c r="I3" s="41"/>
-    </row>
-    <row r="4" spans="1:13" ht="10" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="37" t="s">
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="46"/>
+    </row>
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="11" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="38"/>
-      <c r="G4" s="39" t="s">
+      <c r="B8" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="40"/>
-      <c r="I4" s="41"/>
-    </row>
-    <row r="5" spans="1:13" s="5" customFormat="1" ht="11" customHeight="1">
-      <c r="A5" s="2" t="s">
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="F8" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="3" t="s">
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="49"/>
+    </row>
+    <row r="9" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A9" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="44"/>
-    </row>
-    <row r="6" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A6" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="22"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="28"/>
-    </row>
-    <row r="7" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A7" s="26"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="28"/>
-    </row>
-    <row r="8" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A8" s="26"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="28"/>
-    </row>
-    <row r="9" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A9" s="26"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E9" s="22"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="28"/>
-    </row>
-    <row r="10" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A10" s="26"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="33"/>
+    </row>
+    <row r="10" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A10" s="31"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>17</v>
-      </c>
       <c r="E10" s="22"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="28"/>
-    </row>
-    <row r="11" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A11" s="26"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="33"/>
+    </row>
+    <row r="11" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A11" s="31"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E11" s="22"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="28"/>
-    </row>
-    <row r="12" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A12" s="26"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="33"/>
+    </row>
+    <row r="12" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A12" s="31"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E12" s="22"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="28"/>
-    </row>
-    <row r="13" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A13" s="26"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="33"/>
+    </row>
+    <row r="13" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A13" s="31"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E13" s="22"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="28"/>
-    </row>
-    <row r="14" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A14" s="26"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="33"/>
+    </row>
+    <row r="14" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A14" s="31"/>
       <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="E14" s="22"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="28"/>
-    </row>
-    <row r="15" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A15" s="26"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="33"/>
+    </row>
+    <row r="15" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A15" s="31"/>
       <c r="B15" s="6"/>
+      <c r="C15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="E15" s="22"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="28"/>
-    </row>
-    <row r="16" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A16" s="47" t="s">
-        <v>21</v>
-      </c>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="33"/>
+    </row>
+    <row r="16" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A16" s="31"/>
       <c r="B16" s="6"/>
       <c r="C16" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>22</v>
+        <v>10</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="E16" s="22"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="28"/>
-      <c r="L16" s="48"/>
-      <c r="M16" s="48"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="33"/>
     </row>
     <row r="17" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A17" s="47"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="6"/>
-      <c r="C17" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>23</v>
-      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="8"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="28"/>
-      <c r="L17" s="49"/>
-      <c r="M17" s="49"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="33"/>
     </row>
     <row r="18" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A18" s="47"/>
+      <c r="A18" s="31"/>
       <c r="B18" s="6"/>
-      <c r="C18" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>24</v>
-      </c>
       <c r="E18" s="22"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="28"/>
-      <c r="L18" s="49"/>
-      <c r="M18" s="49"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="33"/>
     </row>
     <row r="19" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A19" s="47"/>
+      <c r="A19" s="51" t="s">
+        <v>19</v>
+      </c>
       <c r="B19" s="6"/>
       <c r="C19" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>25</v>
+        <v>10</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="E19" s="22"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="28"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="33"/>
+      <c r="L19" s="52"/>
+      <c r="M19" s="52"/>
     </row>
     <row r="20" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A20" s="47"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="6"/>
       <c r="C20" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E20" s="22"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="28"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="33"/>
+      <c r="L20" s="53"/>
+      <c r="M20" s="53"/>
     </row>
     <row r="21" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A21" s="47"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E21" s="22"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="28"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="33"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="53"/>
     </row>
     <row r="22" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A22" s="47"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E22" s="22"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="28"/>
-      <c r="L22" s="46"/>
-      <c r="M22" s="46"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="33"/>
     </row>
     <row r="23" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A23" s="47"/>
+      <c r="A23" s="51"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E23" s="22"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="28"/>
-      <c r="L23" s="46"/>
-      <c r="M23" s="46"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="33"/>
     </row>
     <row r="24" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A24" s="47"/>
+      <c r="A24" s="51"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E24" s="22"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="28"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="33"/>
     </row>
     <row r="25" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A25" s="47"/>
+      <c r="A25" s="51"/>
       <c r="B25" s="6"/>
       <c r="C25" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E25" s="22"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="28"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="33"/>
+      <c r="L25" s="50"/>
+      <c r="M25" s="50"/>
     </row>
     <row r="26" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A26" s="47"/>
+      <c r="A26" s="51"/>
       <c r="B26" s="6"/>
       <c r="C26" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E26" s="22"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="28"/>
-      <c r="L26" s="46"/>
-      <c r="M26" s="46"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="33"/>
+      <c r="L26" s="50"/>
+      <c r="M26" s="50"/>
     </row>
     <row r="27" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A27" s="47"/>
+      <c r="A27" s="51"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E27" s="22"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="28"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="33"/>
     </row>
     <row r="28" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A28" s="47"/>
+      <c r="A28" s="51"/>
       <c r="B28" s="6"/>
       <c r="C28" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E28" s="22"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="28"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="33"/>
     </row>
     <row r="29" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A29" s="47"/>
+      <c r="A29" s="51"/>
       <c r="B29" s="6"/>
+      <c r="C29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="E29" s="22"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="28"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="33"/>
+      <c r="L29" s="50"/>
+      <c r="M29" s="50"/>
     </row>
     <row r="30" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A30" s="47" t="s">
-        <v>35</v>
-      </c>
+      <c r="A30" s="51"/>
       <c r="B30" s="6"/>
       <c r="C30" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E30" s="22"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="28"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="33"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
     </row>
     <row r="31" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A31" s="47"/>
+      <c r="A31" s="51"/>
       <c r="B31" s="6"/>
       <c r="C31" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E31" s="22"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="28"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="33"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
     </row>
     <row r="32" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A32" s="47"/>
+      <c r="A32" s="51"/>
       <c r="B32" s="6"/>
-      <c r="C32" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="E32" s="22"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="28"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="33"/>
     </row>
     <row r="33" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A33" s="47"/>
+      <c r="A33" s="51" t="s">
+        <v>33</v>
+      </c>
       <c r="B33" s="6"/>
       <c r="C33" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E33" s="22"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="28"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="33"/>
     </row>
     <row r="34" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A34" s="47"/>
+      <c r="A34" s="51"/>
       <c r="B34" s="6"/>
       <c r="C34" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E34" s="22"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="28"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="33"/>
     </row>
     <row r="35" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A35" s="47"/>
+      <c r="A35" s="51"/>
       <c r="B35" s="6"/>
       <c r="C35" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E35" s="22"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="28"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="33"/>
     </row>
     <row r="36" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A36" s="47"/>
+      <c r="A36" s="51"/>
       <c r="B36" s="6"/>
       <c r="C36" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D36" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E36" s="22"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="33"/>
+    </row>
+    <row r="37" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A37" s="51"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E37" s="22"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="33"/>
+    </row>
+    <row r="38" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A38" s="51"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="22"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="33"/>
+    </row>
+    <row r="39" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A39" s="51"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E39" s="22"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="33"/>
+    </row>
+    <row r="40" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A40" s="51"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E40" s="22"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="33"/>
+    </row>
+    <row r="41" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A41" s="51"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E36" s="22"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="28"/>
-    </row>
-    <row r="37" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A37" s="47"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D37" s="8" t="s">
+      <c r="E41" s="25"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="33"/>
+    </row>
+    <row r="42" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A42" s="51"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E37" s="22"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="28"/>
-    </row>
-    <row r="38" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A38" s="47"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E38" s="25"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="28"/>
-    </row>
-    <row r="39" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A39" s="47"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E39" s="25"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="28"/>
-    </row>
-    <row r="40" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A40" s="47"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E40" s="22"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="28"/>
-    </row>
-    <row r="41" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A41" s="47"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E41" s="22"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="28"/>
-    </row>
-    <row r="42" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A42" s="47"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E42" s="22"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
-      <c r="H42" s="27"/>
-      <c r="I42" s="28"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="33"/>
     </row>
     <row r="43" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A43" s="47"/>
+      <c r="A43" s="51"/>
       <c r="B43" s="6"/>
       <c r="C43" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E43" s="22"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="28"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="33"/>
     </row>
     <row r="44" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A44" s="47"/>
+      <c r="A44" s="51"/>
       <c r="B44" s="6"/>
       <c r="C44" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E44" s="22"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="28"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="33"/>
     </row>
     <row r="45" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A45" s="47"/>
+      <c r="A45" s="51"/>
       <c r="B45" s="6"/>
       <c r="C45" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E45" s="22"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="28"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="33"/>
     </row>
     <row r="46" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A46" s="47"/>
+      <c r="A46" s="51"/>
       <c r="B46" s="6"/>
       <c r="C46" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E46" s="22"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="28"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="33"/>
     </row>
     <row r="47" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A47" s="47"/>
+      <c r="A47" s="51"/>
       <c r="B47" s="6"/>
       <c r="C47" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E47" s="22"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="27"/>
-      <c r="I47" s="28"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="33"/>
     </row>
     <row r="48" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A48" s="47"/>
+      <c r="A48" s="51"/>
       <c r="B48" s="6"/>
       <c r="C48" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E48" s="22"/>
-      <c r="F48" s="27"/>
-      <c r="G48" s="27"/>
-      <c r="H48" s="27"/>
-      <c r="I48" s="28"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="33"/>
     </row>
     <row r="49" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A49" s="47"/>
+      <c r="A49" s="51"/>
       <c r="B49" s="6"/>
       <c r="C49" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D49" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E49" s="22"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="33"/>
+    </row>
+    <row r="50" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A50" s="51"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E50" s="22"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="33"/>
+    </row>
+    <row r="51" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A51" s="51"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E51" s="22"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="33"/>
+    </row>
+    <row r="52" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A52" s="51"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E52" s="22"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="33"/>
+    </row>
+    <row r="53" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A53" s="51"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E53" s="22"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="33"/>
+    </row>
+    <row r="54" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A54" s="51"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="33"/>
+    </row>
+    <row r="55" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A55" s="51"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="33"/>
+    </row>
+    <row r="56" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A56" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="22"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="28"/>
-    </row>
-    <row r="50" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A50" s="47"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D50" s="16" t="s">
+      <c r="B56" s="6"/>
+      <c r="C56" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="E50" s="22"/>
-      <c r="F50" s="27"/>
-      <c r="G50" s="27"/>
-      <c r="H50" s="27"/>
-      <c r="I50" s="28"/>
-    </row>
-    <row r="51" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A51" s="47"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="27"/>
-      <c r="H51" s="27"/>
-      <c r="I51" s="28"/>
-    </row>
-    <row r="52" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A52" s="47"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="18"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="28"/>
-    </row>
-    <row r="53" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A53" s="50" t="s">
+      <c r="D56" s="55"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="33"/>
+    </row>
+    <row r="57" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A57" s="54"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="B53" s="6"/>
-      <c r="C53" s="51" t="s">
+      <c r="D57" s="55"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="33"/>
+    </row>
+    <row r="58" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A58" s="54"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="D53" s="51"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="27"/>
-      <c r="G53" s="27"/>
-      <c r="H53" s="27"/>
-      <c r="I53" s="28"/>
-    </row>
-    <row r="54" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A54" s="50"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="51" t="s">
+      <c r="D58" s="55"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="33"/>
+    </row>
+    <row r="59" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
+      <c r="A59" s="54"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="D54" s="51"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="27"/>
-      <c r="H54" s="27"/>
-      <c r="I54" s="28"/>
-    </row>
-    <row r="55" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A55" s="50"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="D55" s="51"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="28"/>
-    </row>
-    <row r="56" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A56" s="50"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="51" t="s">
-        <v>61</v>
-      </c>
-      <c r="D56" s="51"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="27"/>
-      <c r="G56" s="27"/>
-      <c r="H56" s="27"/>
-      <c r="I56" s="28"/>
-    </row>
-    <row r="57" spans="1:9" ht="9" customHeight="1">
-      <c r="A57" s="58"/>
-      <c r="B57" s="19"/>
-      <c r="C57" s="60"/>
-      <c r="D57" s="61"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="62"/>
-      <c r="G57" s="62"/>
-      <c r="H57" s="62"/>
-      <c r="I57" s="63"/>
-    </row>
-    <row r="58" spans="1:9" ht="9" customHeight="1">
-      <c r="A58" s="58"/>
-      <c r="B58" s="19"/>
-      <c r="C58" s="60"/>
-      <c r="D58" s="61"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="64"/>
-      <c r="G58" s="64"/>
-      <c r="H58" s="64"/>
-      <c r="I58" s="65"/>
-    </row>
-    <row r="59" spans="1:9" ht="9" customHeight="1">
-      <c r="A59" s="58"/>
-      <c r="B59" s="19"/>
-      <c r="C59" s="60"/>
-      <c r="D59" s="61"/>
-      <c r="E59" s="23"/>
-      <c r="F59" s="52"/>
-      <c r="G59" s="52"/>
-      <c r="H59" s="52"/>
-      <c r="I59" s="53"/>
+      <c r="D59" s="55"/>
+      <c r="E59" s="25"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+      <c r="I59" s="33"/>
     </row>
     <row r="60" spans="1:9" ht="9" customHeight="1">
-      <c r="A60" s="58"/>
+      <c r="A60" s="71"/>
       <c r="B60" s="19"/>
-      <c r="C60" s="60"/>
-      <c r="D60" s="61"/>
-      <c r="E60" s="23"/>
-      <c r="F60" s="52"/>
-      <c r="G60" s="52"/>
-      <c r="H60" s="52"/>
-      <c r="I60" s="53"/>
+      <c r="C60" s="73"/>
+      <c r="D60" s="74"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="75"/>
+      <c r="G60" s="75"/>
+      <c r="H60" s="75"/>
+      <c r="I60" s="76"/>
     </row>
     <row r="61" spans="1:9" ht="9" customHeight="1">
-      <c r="A61" s="59"/>
+      <c r="A61" s="71"/>
       <c r="B61" s="19"/>
-      <c r="C61" s="60"/>
-      <c r="D61" s="61"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="52"/>
-      <c r="G61" s="52"/>
-      <c r="H61" s="52"/>
-      <c r="I61" s="53"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="74"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="77"/>
+      <c r="G61" s="77"/>
+      <c r="H61" s="77"/>
+      <c r="I61" s="78"/>
     </row>
     <row r="62" spans="1:9" ht="9" customHeight="1">
-      <c r="A62" s="70" t="s">
-        <v>62</v>
-      </c>
-      <c r="B62" s="71"/>
-      <c r="C62" s="71"/>
-      <c r="D62" s="72"/>
-      <c r="E62" s="54" t="s">
-        <v>63</v>
-      </c>
-      <c r="F62" s="54"/>
-      <c r="G62" s="54"/>
-      <c r="H62" s="54"/>
-      <c r="I62" s="55"/>
+      <c r="A62" s="71"/>
+      <c r="B62" s="19"/>
+      <c r="C62" s="73"/>
+      <c r="D62" s="74"/>
+      <c r="E62" s="23"/>
+      <c r="F62" s="56"/>
+      <c r="G62" s="56"/>
+      <c r="H62" s="56"/>
+      <c r="I62" s="57"/>
     </row>
     <row r="63" spans="1:9" ht="9" customHeight="1">
-      <c r="A63" s="73"/>
-      <c r="B63" s="74"/>
-      <c r="C63" s="74"/>
-      <c r="D63" s="75"/>
-      <c r="E63" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="F63" s="43"/>
-      <c r="G63" s="43"/>
-      <c r="H63" s="43"/>
-      <c r="I63" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="A63" s="71"/>
+      <c r="B63" s="19"/>
+      <c r="C63" s="73"/>
+      <c r="D63" s="74"/>
+      <c r="E63" s="23"/>
+      <c r="F63" s="56"/>
+      <c r="G63" s="56"/>
+      <c r="H63" s="56"/>
+      <c r="I63" s="57"/>
     </row>
     <row r="64" spans="1:9" ht="9" customHeight="1">
-      <c r="A64" s="73"/>
-      <c r="B64" s="74"/>
-      <c r="C64" s="74"/>
-      <c r="D64" s="75"/>
-      <c r="E64" s="56"/>
+      <c r="A64" s="72"/>
+      <c r="B64" s="19"/>
+      <c r="C64" s="73"/>
+      <c r="D64" s="74"/>
+      <c r="E64" s="23"/>
       <c r="F64" s="56"/>
       <c r="G64" s="56"/>
       <c r="H64" s="56"/>
-      <c r="I64" s="20"/>
+      <c r="I64" s="57"/>
     </row>
     <row r="65" spans="1:9" ht="9" customHeight="1">
-      <c r="A65" s="73"/>
-      <c r="B65" s="74"/>
-      <c r="C65" s="74"/>
-      <c r="D65" s="75"/>
-      <c r="E65" s="56"/>
-      <c r="F65" s="56"/>
-      <c r="G65" s="56"/>
-      <c r="H65" s="56"/>
-      <c r="I65" s="20"/>
+      <c r="A65" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="B65" s="59"/>
+      <c r="C65" s="59"/>
+      <c r="D65" s="60"/>
+      <c r="E65" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="F65" s="67"/>
+      <c r="G65" s="67"/>
+      <c r="H65" s="67"/>
+      <c r="I65" s="68"/>
     </row>
     <row r="66" spans="1:9" ht="9" customHeight="1">
-      <c r="A66" s="73"/>
-      <c r="B66" s="74"/>
-      <c r="C66" s="74"/>
-      <c r="D66" s="75"/>
-      <c r="E66" s="56"/>
-      <c r="F66" s="56"/>
-      <c r="G66" s="56"/>
-      <c r="H66" s="56"/>
-      <c r="I66" s="20"/>
+      <c r="A66" s="61"/>
+      <c r="B66" s="62"/>
+      <c r="C66" s="62"/>
+      <c r="D66" s="63"/>
+      <c r="E66" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="4" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="67" spans="1:9" ht="9" customHeight="1">
-      <c r="A67" s="73"/>
-      <c r="B67" s="74"/>
-      <c r="C67" s="74"/>
-      <c r="D67" s="75"/>
-      <c r="E67" s="56"/>
-      <c r="F67" s="56"/>
-      <c r="G67" s="56"/>
-      <c r="H67" s="56"/>
+      <c r="A67" s="61"/>
+      <c r="B67" s="62"/>
+      <c r="C67" s="62"/>
+      <c r="D67" s="63"/>
+      <c r="E67" s="69"/>
+      <c r="F67" s="69"/>
+      <c r="G67" s="69"/>
+      <c r="H67" s="69"/>
       <c r="I67" s="20"/>
     </row>
     <row r="68" spans="1:9" ht="9" customHeight="1">
-      <c r="A68" s="73"/>
-      <c r="B68" s="74"/>
-      <c r="C68" s="74"/>
-      <c r="D68" s="75"/>
-      <c r="E68" s="56"/>
-      <c r="F68" s="56"/>
-      <c r="G68" s="56"/>
-      <c r="H68" s="56"/>
+      <c r="A68" s="61"/>
+      <c r="B68" s="62"/>
+      <c r="C68" s="62"/>
+      <c r="D68" s="63"/>
+      <c r="E68" s="69"/>
+      <c r="F68" s="69"/>
+      <c r="G68" s="69"/>
+      <c r="H68" s="69"/>
       <c r="I68" s="20"/>
     </row>
     <row r="69" spans="1:9" ht="9" customHeight="1">
-      <c r="A69" s="73"/>
-      <c r="B69" s="74"/>
-      <c r="C69" s="74"/>
-      <c r="D69" s="75"/>
-      <c r="E69" s="57" t="s">
+      <c r="A69" s="61"/>
+      <c r="B69" s="62"/>
+      <c r="C69" s="62"/>
+      <c r="D69" s="63"/>
+      <c r="E69" s="69"/>
+      <c r="F69" s="69"/>
+      <c r="G69" s="69"/>
+      <c r="H69" s="69"/>
+      <c r="I69" s="20"/>
+    </row>
+    <row r="70" spans="1:9" ht="9" customHeight="1">
+      <c r="A70" s="61"/>
+      <c r="B70" s="62"/>
+      <c r="C70" s="62"/>
+      <c r="D70" s="63"/>
+      <c r="E70" s="69"/>
+      <c r="F70" s="69"/>
+      <c r="G70" s="69"/>
+      <c r="H70" s="69"/>
+      <c r="I70" s="20"/>
+    </row>
+    <row r="71" spans="1:9" ht="9" customHeight="1">
+      <c r="A71" s="61"/>
+      <c r="B71" s="62"/>
+      <c r="C71" s="62"/>
+      <c r="D71" s="63"/>
+      <c r="E71" s="69"/>
+      <c r="F71" s="69"/>
+      <c r="G71" s="69"/>
+      <c r="H71" s="69"/>
+      <c r="I71" s="20"/>
+    </row>
+    <row r="72" spans="1:9" ht="9" customHeight="1">
+      <c r="A72" s="61"/>
+      <c r="B72" s="62"/>
+      <c r="C72" s="62"/>
+      <c r="D72" s="63"/>
+      <c r="E72" s="70" t="s">
+        <v>64</v>
+      </c>
+      <c r="F72" s="70"/>
+      <c r="G72" s="70"/>
+      <c r="H72" s="32"/>
+      <c r="I72" s="33"/>
+    </row>
+    <row r="73" spans="1:9" ht="9" customHeight="1">
+      <c r="A73" s="61"/>
+      <c r="B73" s="62"/>
+      <c r="C73" s="62"/>
+      <c r="D73" s="63"/>
+      <c r="E73" s="70" t="s">
+        <v>65</v>
+      </c>
+      <c r="F73" s="70"/>
+      <c r="G73" s="70"/>
+      <c r="H73" s="32"/>
+      <c r="I73" s="33"/>
+    </row>
+    <row r="74" spans="1:9" ht="9" customHeight="1">
+      <c r="A74" s="61"/>
+      <c r="B74" s="62"/>
+      <c r="C74" s="62"/>
+      <c r="D74" s="63"/>
+      <c r="E74" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="F69" s="57"/>
-      <c r="G69" s="57"/>
-      <c r="H69" s="27"/>
-      <c r="I69" s="28"/>
-    </row>
-    <row r="70" spans="1:9" ht="9" customHeight="1">
-      <c r="A70" s="73"/>
-      <c r="B70" s="74"/>
-      <c r="C70" s="74"/>
-      <c r="D70" s="75"/>
-      <c r="E70" s="57" t="s">
+      <c r="F74" s="70"/>
+      <c r="G74" s="70"/>
+      <c r="H74" s="32"/>
+      <c r="I74" s="33"/>
+    </row>
+    <row r="75" spans="1:9" ht="9" customHeight="1">
+      <c r="A75" s="61"/>
+      <c r="B75" s="62"/>
+      <c r="C75" s="62"/>
+      <c r="D75" s="63"/>
+      <c r="E75" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="F70" s="57"/>
-      <c r="G70" s="57"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="28"/>
-    </row>
-    <row r="71" spans="1:9" ht="9" customHeight="1">
-      <c r="A71" s="73"/>
-      <c r="B71" s="74"/>
-      <c r="C71" s="74"/>
-      <c r="D71" s="75"/>
-      <c r="E71" s="57" t="s">
+      <c r="F75" s="70"/>
+      <c r="G75" s="70"/>
+      <c r="H75" s="32"/>
+      <c r="I75" s="33"/>
+    </row>
+    <row r="76" spans="1:9" ht="9" customHeight="1">
+      <c r="A76" s="61"/>
+      <c r="B76" s="62"/>
+      <c r="C76" s="62"/>
+      <c r="D76" s="63"/>
+      <c r="E76" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="F71" s="57"/>
-      <c r="G71" s="57"/>
-      <c r="H71" s="27"/>
-      <c r="I71" s="28"/>
-    </row>
-    <row r="72" spans="1:9" ht="9" customHeight="1">
-      <c r="A72" s="73"/>
-      <c r="B72" s="74"/>
-      <c r="C72" s="74"/>
-      <c r="D72" s="75"/>
-      <c r="E72" s="57" t="s">
+      <c r="F76" s="70"/>
+      <c r="G76" s="70"/>
+      <c r="H76" s="32"/>
+      <c r="I76" s="33"/>
+    </row>
+    <row r="77" spans="1:9" ht="9" customHeight="1" thickBot="1">
+      <c r="A77" s="64"/>
+      <c r="B77" s="65"/>
+      <c r="C77" s="65"/>
+      <c r="D77" s="66"/>
+      <c r="E77" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="F72" s="57"/>
-      <c r="G72" s="57"/>
-      <c r="H72" s="27"/>
-      <c r="I72" s="28"/>
-    </row>
-    <row r="73" spans="1:9" ht="9" customHeight="1">
-      <c r="A73" s="73"/>
-      <c r="B73" s="74"/>
-      <c r="C73" s="74"/>
-      <c r="D73" s="75"/>
-      <c r="E73" s="57" t="s">
+      <c r="F77" s="82"/>
+      <c r="G77" s="82"/>
+      <c r="H77" s="80"/>
+      <c r="I77" s="81"/>
+    </row>
+    <row r="78" spans="1:9" ht="9" customHeight="1" thickTop="1">
+      <c r="G78" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="F73" s="57"/>
-      <c r="G73" s="57"/>
-      <c r="H73" s="27"/>
-      <c r="I73" s="28"/>
-    </row>
-    <row r="74" spans="1:9" ht="9" customHeight="1" thickBot="1">
-      <c r="A74" s="76"/>
-      <c r="B74" s="77"/>
-      <c r="C74" s="77"/>
-      <c r="D74" s="78"/>
-      <c r="E74" s="69" t="s">
-        <v>71</v>
-      </c>
-      <c r="F74" s="69"/>
-      <c r="G74" s="69"/>
-      <c r="H74" s="67"/>
-      <c r="I74" s="68"/>
-    </row>
-    <row r="75" spans="1:9" ht="9" customHeight="1" thickTop="1">
-      <c r="G75" s="66" t="s">
-        <v>72</v>
-      </c>
-      <c r="H75" s="66"/>
-      <c r="I75" s="66"/>
-    </row>
-    <row r="76" spans="1:9" ht="9" customHeight="1">
-      <c r="A76"/>
-      <c r="B76"/>
-      <c r="C76"/>
-      <c r="D76"/>
-      <c r="E76"/>
-      <c r="F76"/>
-      <c r="G76"/>
-      <c r="H76"/>
-      <c r="I76"/>
-    </row>
-    <row r="77" spans="1:9">
-      <c r="A77"/>
-      <c r="B77"/>
-      <c r="C77"/>
-      <c r="D77"/>
-      <c r="E77"/>
-      <c r="F77"/>
-      <c r="G77"/>
-      <c r="H77"/>
-      <c r="I77"/>
-    </row>
-    <row r="78" spans="1:9">
-      <c r="A78"/>
-      <c r="B78"/>
-      <c r="C78"/>
-      <c r="D78"/>
-      <c r="E78"/>
-      <c r="F78"/>
-      <c r="G78"/>
-      <c r="H78"/>
-      <c r="I78"/>
-    </row>
-    <row r="79" spans="1:9">
+      <c r="H78" s="79"/>
+      <c r="I78" s="79"/>
+    </row>
+    <row r="79" spans="1:9" ht="9" customHeight="1">
       <c r="A79"/>
       <c r="B79"/>
       <c r="C79"/>
@@ -2400,113 +2450,125 @@
     <row r="81" customFormat="1"/>
     <row r="82" customFormat="1"/>
     <row r="83" customFormat="1"/>
+    <row r="84" customFormat="1"/>
+    <row r="85" customFormat="1"/>
+    <row r="86" customFormat="1"/>
   </sheetData>
-  <mergeCells count="105">
-    <mergeCell ref="G75:I75"/>
-    <mergeCell ref="H69:I70"/>
-    <mergeCell ref="E70:G70"/>
-    <mergeCell ref="E71:G71"/>
-    <mergeCell ref="H71:I72"/>
-    <mergeCell ref="E72:G72"/>
+  <mergeCells count="114">
+    <mergeCell ref="G78:I78"/>
+    <mergeCell ref="H72:I73"/>
     <mergeCell ref="E73:G73"/>
-    <mergeCell ref="H73:I74"/>
     <mergeCell ref="E74:G74"/>
-    <mergeCell ref="F61:I61"/>
-    <mergeCell ref="A62:D74"/>
-    <mergeCell ref="E62:I62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="H74:I75"/>
+    <mergeCell ref="E75:G75"/>
+    <mergeCell ref="E76:G76"/>
+    <mergeCell ref="H76:I77"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="F64:I64"/>
+    <mergeCell ref="A65:D77"/>
+    <mergeCell ref="E65:I65"/>
     <mergeCell ref="E66:H66"/>
     <mergeCell ref="E67:H67"/>
     <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:G69"/>
-    <mergeCell ref="A57:A61"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E72:G72"/>
+    <mergeCell ref="A60:A64"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="F61:I61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="F62:I62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="A56:A59"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="F56:I56"/>
     <mergeCell ref="C57:D57"/>
     <mergeCell ref="F57:I57"/>
     <mergeCell ref="C58:D58"/>
     <mergeCell ref="F58:I58"/>
     <mergeCell ref="C59:D59"/>
     <mergeCell ref="F59:I59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="A33:A55"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F51:I51"/>
     <mergeCell ref="F52:I52"/>
-    <mergeCell ref="A53:A56"/>
-    <mergeCell ref="C53:D53"/>
     <mergeCell ref="F53:I53"/>
-    <mergeCell ref="C54:D54"/>
     <mergeCell ref="F54:I54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="A30:A52"/>
+    <mergeCell ref="F43:I43"/>
+    <mergeCell ref="F44:I44"/>
+    <mergeCell ref="F45:I45"/>
     <mergeCell ref="F46:I46"/>
     <mergeCell ref="F47:I47"/>
     <mergeCell ref="F48:I48"/>
-    <mergeCell ref="F49:I49"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="F39:I39"/>
     <mergeCell ref="F40:I40"/>
     <mergeCell ref="F41:I41"/>
     <mergeCell ref="F42:I42"/>
-    <mergeCell ref="F43:I43"/>
-    <mergeCell ref="F44:I44"/>
-    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="F30:I30"/>
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="F34:I34"/>
     <mergeCell ref="F35:I35"/>
     <mergeCell ref="F36:I36"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L25:M25"/>
     <mergeCell ref="F26:I26"/>
     <mergeCell ref="L26:M26"/>
     <mergeCell ref="F27:I27"/>
     <mergeCell ref="F28:I28"/>
-    <mergeCell ref="F29:I29"/>
-    <mergeCell ref="F30:I30"/>
-    <mergeCell ref="F31:I31"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="A19:A32"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="L21:M21"/>
     <mergeCell ref="F22:I22"/>
-    <mergeCell ref="L22:M22"/>
     <mergeCell ref="F23:I23"/>
-    <mergeCell ref="L23:M23"/>
     <mergeCell ref="F24:I24"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="A16:A29"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="A6:A15"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="A9:A18"/>
     <mergeCell ref="F9:I9"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="F12:I12"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="D2:I2"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:I3"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="F12:I12"/>
     <mergeCell ref="F13:I13"/>
     <mergeCell ref="F14:I14"/>
     <mergeCell ref="F15:I15"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E5:F5"/>
     <mergeCell ref="G4:I4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.43263888888888902" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/maintenance/electric_engine.xlsx
+++ b/public/assets/templates/maintenance/electric_engine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC6B1D4-6BBE-4CD9-A85F-D187281B8196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145EF4E8-AA66-429C-A460-869D27E4030F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{7A80608D-5162-4C69-AACA-06EF8CFA5F02}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="80">
   <si>
     <t>LAPORAN MAINTENANCE ELECTRIC ENGINE</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>Departemen</t>
+  </si>
+  <si>
+    <t>MID</t>
   </si>
 </sst>
 </file>
@@ -672,7 +675,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -757,173 +760,176 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1308,30 +1314,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickTop="1">
-      <c r="A1" s="34"/>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="38" t="s">
+      <c r="A1" s="64"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="39"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="69"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="36"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="41"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="71"/>
     </row>
     <row r="3" spans="1:9" ht="10" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -1340,17 +1346,17 @@
       <c r="B3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="42" t="s">
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="43"/>
-      <c r="G3" s="29" t="s">
+      <c r="F3" s="73"/>
+      <c r="G3" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="30"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="75"/>
     </row>
     <row r="4" spans="1:9" ht="10" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -1359,17 +1365,17 @@
       <c r="B4" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28" t="s">
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="28"/>
-      <c r="G4" s="29" t="s">
+      <c r="F4" s="81"/>
+      <c r="G4" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="H4" s="29"/>
-      <c r="I4" s="30"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="75"/>
     </row>
     <row r="5" spans="1:9" ht="10" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -1378,17 +1384,17 @@
       <c r="B5" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28" t="s">
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="F5" s="28"/>
-      <c r="G5" s="29" t="s">
+      <c r="F5" s="81"/>
+      <c r="G5" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="H5" s="29"/>
-      <c r="I5" s="30"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="75"/>
     </row>
     <row r="6" spans="1:9" ht="10" customHeight="1">
       <c r="A6" s="1" t="s">
@@ -1397,17 +1403,17 @@
       <c r="B6" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="42" t="s">
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="29" t="s">
+      <c r="F6" s="73"/>
+      <c r="G6" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="H6" s="29"/>
-      <c r="I6" s="30"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="75"/>
     </row>
     <row r="7" spans="1:9" ht="10" customHeight="1">
       <c r="A7" s="1" t="s">
@@ -1416,23 +1422,23 @@
       <c r="B7" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="46"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="78"/>
     </row>
     <row r="8" spans="1:9" s="5" customFormat="1" ht="11" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
+      <c r="C8" s="79"/>
+      <c r="D8" s="79"/>
       <c r="E8" s="3" t="s">
         <v>7</v>
       </c>
@@ -1441,10 +1447,10 @@
       </c>
       <c r="G8" s="48"/>
       <c r="H8" s="48"/>
-      <c r="I8" s="49"/>
+      <c r="I8" s="80"/>
     </row>
     <row r="9" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="63" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="6"/>
@@ -1455,13 +1461,13 @@
         <v>11</v>
       </c>
       <c r="E9" s="22"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="33"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="30"/>
     </row>
     <row r="10" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A10" s="31"/>
+      <c r="A10" s="63"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
         <v>10</v>
@@ -1470,13 +1476,13 @@
         <v>12</v>
       </c>
       <c r="E10" s="22"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="33"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="30"/>
     </row>
     <row r="11" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A11" s="31"/>
+      <c r="A11" s="63"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7" t="s">
         <v>10</v>
@@ -1485,13 +1491,13 @@
         <v>13</v>
       </c>
       <c r="E11" s="22"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="33"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="30"/>
     </row>
     <row r="12" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A12" s="31"/>
+      <c r="A12" s="63"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7" t="s">
         <v>10</v>
@@ -1500,13 +1506,13 @@
         <v>14</v>
       </c>
       <c r="E12" s="22"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="33"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="30"/>
     </row>
     <row r="13" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A13" s="31"/>
+      <c r="A13" s="63"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7" t="s">
         <v>10</v>
@@ -1515,13 +1521,13 @@
         <v>15</v>
       </c>
       <c r="E13" s="22"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="33"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="30"/>
     </row>
     <row r="14" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A14" s="31"/>
+      <c r="A14" s="63"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7" t="s">
         <v>10</v>
@@ -1530,13 +1536,13 @@
         <v>16</v>
       </c>
       <c r="E14" s="22"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="33"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="30"/>
     </row>
     <row r="15" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A15" s="31"/>
+      <c r="A15" s="63"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7" t="s">
         <v>10</v>
@@ -1545,13 +1551,13 @@
         <v>17</v>
       </c>
       <c r="E15" s="22"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="33"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="30"/>
     </row>
     <row r="16" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A16" s="31"/>
+      <c r="A16" s="63"/>
       <c r="B16" s="6"/>
       <c r="C16" s="7" t="s">
         <v>10</v>
@@ -1560,33 +1566,33 @@
         <v>18</v>
       </c>
       <c r="E16" s="22"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="33"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="30"/>
     </row>
     <row r="17" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A17" s="31"/>
+      <c r="A17" s="63"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
       <c r="D17" s="8"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="33"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="30"/>
     </row>
     <row r="18" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A18" s="31"/>
+      <c r="A18" s="63"/>
       <c r="B18" s="6"/>
       <c r="E18" s="22"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="33"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="30"/>
     </row>
     <row r="19" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A19" s="51" t="s">
+      <c r="A19" s="59" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="6"/>
@@ -1597,15 +1603,15 @@
         <v>20</v>
       </c>
       <c r="E19" s="22"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="33"/>
-      <c r="L19" s="52"/>
-      <c r="M19" s="52"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="30"/>
+      <c r="L19" s="61"/>
+      <c r="M19" s="61"/>
     </row>
     <row r="20" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A20" s="51"/>
+      <c r="A20" s="59"/>
       <c r="B20" s="6"/>
       <c r="C20" s="7" t="s">
         <v>10</v>
@@ -1614,15 +1620,15 @@
         <v>21</v>
       </c>
       <c r="E20" s="22"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="33"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="53"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="30"/>
+      <c r="L20" s="62"/>
+      <c r="M20" s="62"/>
     </row>
     <row r="21" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A21" s="51"/>
+      <c r="A21" s="59"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7" t="s">
         <v>10</v>
@@ -1631,15 +1637,15 @@
         <v>22</v>
       </c>
       <c r="E21" s="22"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="33"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="53"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="30"/>
+      <c r="L21" s="62"/>
+      <c r="M21" s="62"/>
     </row>
     <row r="22" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A22" s="51"/>
+      <c r="A22" s="59"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7" t="s">
         <v>10</v>
@@ -1648,13 +1654,13 @@
         <v>23</v>
       </c>
       <c r="E22" s="22"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="33"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="30"/>
     </row>
     <row r="23" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A23" s="51"/>
+      <c r="A23" s="59"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7" t="s">
         <v>10</v>
@@ -1663,13 +1669,13 @@
         <v>24</v>
       </c>
       <c r="E23" s="22"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="33"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="30"/>
     </row>
     <row r="24" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A24" s="51"/>
+      <c r="A24" s="59"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7" t="s">
         <v>10</v>
@@ -1678,13 +1684,13 @@
         <v>25</v>
       </c>
       <c r="E24" s="22"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="33"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="30"/>
     </row>
     <row r="25" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A25" s="51"/>
+      <c r="A25" s="59"/>
       <c r="B25" s="6"/>
       <c r="C25" s="7" t="s">
         <v>10</v>
@@ -1693,15 +1699,15 @@
         <v>26</v>
       </c>
       <c r="E25" s="22"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="33"/>
-      <c r="L25" s="50"/>
-      <c r="M25" s="50"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="30"/>
+      <c r="L25" s="60"/>
+      <c r="M25" s="60"/>
     </row>
     <row r="26" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A26" s="51"/>
+      <c r="A26" s="59"/>
       <c r="B26" s="6"/>
       <c r="C26" s="7" t="s">
         <v>10</v>
@@ -1710,15 +1716,15 @@
         <v>27</v>
       </c>
       <c r="E26" s="22"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="33"/>
-      <c r="L26" s="50"/>
-      <c r="M26" s="50"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="30"/>
+      <c r="L26" s="60"/>
+      <c r="M26" s="60"/>
     </row>
     <row r="27" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A27" s="51"/>
+      <c r="A27" s="59"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7" t="s">
         <v>10</v>
@@ -1727,13 +1733,13 @@
         <v>28</v>
       </c>
       <c r="E27" s="22"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="33"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="30"/>
     </row>
     <row r="28" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A28" s="51"/>
+      <c r="A28" s="59"/>
       <c r="B28" s="6"/>
       <c r="C28" s="7" t="s">
         <v>10</v>
@@ -1742,13 +1748,13 @@
         <v>29</v>
       </c>
       <c r="E28" s="22"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="33"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="30"/>
     </row>
     <row r="29" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A29" s="51"/>
+      <c r="A29" s="59"/>
       <c r="B29" s="6"/>
       <c r="C29" s="7" t="s">
         <v>10</v>
@@ -1757,15 +1763,15 @@
         <v>30</v>
       </c>
       <c r="E29" s="22"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="33"/>
-      <c r="L29" s="50"/>
-      <c r="M29" s="50"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="30"/>
+      <c r="L29" s="60"/>
+      <c r="M29" s="60"/>
     </row>
     <row r="30" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A30" s="51"/>
+      <c r="A30" s="59"/>
       <c r="B30" s="6"/>
       <c r="C30" s="7" t="s">
         <v>10</v>
@@ -1774,15 +1780,15 @@
         <v>31</v>
       </c>
       <c r="E30" s="22"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="33"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="30"/>
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
     </row>
     <row r="31" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A31" s="51"/>
+      <c r="A31" s="59"/>
       <c r="B31" s="6"/>
       <c r="C31" s="7" t="s">
         <v>10</v>
@@ -1791,24 +1797,24 @@
         <v>32</v>
       </c>
       <c r="E31" s="22"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="33"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="30"/>
       <c r="L31" s="11"/>
       <c r="M31" s="11"/>
     </row>
     <row r="32" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A32" s="51"/>
+      <c r="A32" s="59"/>
       <c r="B32" s="6"/>
       <c r="E32" s="22"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="33"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="30"/>
     </row>
     <row r="33" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A33" s="51" t="s">
+      <c r="A33" s="59" t="s">
         <v>33</v>
       </c>
       <c r="B33" s="6"/>
@@ -1819,13 +1825,13 @@
         <v>34</v>
       </c>
       <c r="E33" s="22"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="33"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="30"/>
     </row>
     <row r="34" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A34" s="51"/>
+      <c r="A34" s="59"/>
       <c r="B34" s="6"/>
       <c r="C34" s="7" t="s">
         <v>10</v>
@@ -1834,13 +1840,13 @@
         <v>35</v>
       </c>
       <c r="E34" s="22"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="33"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="30"/>
     </row>
     <row r="35" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A35" s="51"/>
+      <c r="A35" s="59"/>
       <c r="B35" s="6"/>
       <c r="C35" s="7" t="s">
         <v>10</v>
@@ -1849,13 +1855,13 @@
         <v>36</v>
       </c>
       <c r="E35" s="22"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="33"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="30"/>
     </row>
     <row r="36" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A36" s="51"/>
+      <c r="A36" s="59"/>
       <c r="B36" s="6"/>
       <c r="C36" s="7" t="s">
         <v>10</v>
@@ -1864,13 +1870,13 @@
         <v>37</v>
       </c>
       <c r="E36" s="22"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="33"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="30"/>
     </row>
     <row r="37" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A37" s="51"/>
+      <c r="A37" s="59"/>
       <c r="B37" s="6"/>
       <c r="C37" s="7" t="s">
         <v>10</v>
@@ -1879,13 +1885,13 @@
         <v>38</v>
       </c>
       <c r="E37" s="22"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="33"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="30"/>
     </row>
     <row r="38" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A38" s="51"/>
+      <c r="A38" s="59"/>
       <c r="B38" s="6"/>
       <c r="C38" s="7" t="s">
         <v>10</v>
@@ -1894,13 +1900,13 @@
         <v>39</v>
       </c>
       <c r="E38" s="22"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="33"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="30"/>
     </row>
     <row r="39" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A39" s="51"/>
+      <c r="A39" s="59"/>
       <c r="B39" s="6"/>
       <c r="C39" s="7" t="s">
         <v>10</v>
@@ -1909,13 +1915,13 @@
         <v>40</v>
       </c>
       <c r="E39" s="22"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="33"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="30"/>
     </row>
     <row r="40" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A40" s="51"/>
+      <c r="A40" s="59"/>
       <c r="B40" s="13"/>
       <c r="C40" s="7" t="s">
         <v>10</v>
@@ -1924,13 +1930,13 @@
         <v>41</v>
       </c>
       <c r="E40" s="22"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="33"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="30"/>
     </row>
     <row r="41" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A41" s="51"/>
+      <c r="A41" s="59"/>
       <c r="B41" s="13"/>
       <c r="C41" s="7" t="s">
         <v>10</v>
@@ -1939,13 +1945,13 @@
         <v>42</v>
       </c>
       <c r="E41" s="25"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="33"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+      <c r="I41" s="30"/>
     </row>
     <row r="42" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A42" s="51"/>
+      <c r="A42" s="59"/>
       <c r="B42" s="13"/>
       <c r="C42" s="7" t="s">
         <v>10</v>
@@ -1954,13 +1960,13 @@
         <v>43</v>
       </c>
       <c r="E42" s="25"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="33"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="30"/>
     </row>
     <row r="43" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A43" s="51"/>
+      <c r="A43" s="59"/>
       <c r="B43" s="6"/>
       <c r="C43" s="7" t="s">
         <v>10</v>
@@ -1969,13 +1975,13 @@
         <v>44</v>
       </c>
       <c r="E43" s="22"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="33"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="30"/>
     </row>
     <row r="44" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A44" s="51"/>
+      <c r="A44" s="59"/>
       <c r="B44" s="6"/>
       <c r="C44" s="7" t="s">
         <v>10</v>
@@ -1984,13 +1990,13 @@
         <v>45</v>
       </c>
       <c r="E44" s="22"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="33"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="30"/>
     </row>
     <row r="45" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A45" s="51"/>
+      <c r="A45" s="59"/>
       <c r="B45" s="6"/>
       <c r="C45" s="7" t="s">
         <v>10</v>
@@ -1999,13 +2005,13 @@
         <v>46</v>
       </c>
       <c r="E45" s="22"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
-      <c r="I45" s="33"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
+      <c r="I45" s="30"/>
     </row>
     <row r="46" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A46" s="51"/>
+      <c r="A46" s="59"/>
       <c r="B46" s="6"/>
       <c r="C46" s="7" t="s">
         <v>10</v>
@@ -2014,13 +2020,13 @@
         <v>47</v>
       </c>
       <c r="E46" s="22"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32"/>
-      <c r="I46" s="33"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="30"/>
     </row>
     <row r="47" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A47" s="51"/>
+      <c r="A47" s="59"/>
       <c r="B47" s="6"/>
       <c r="C47" s="7" t="s">
         <v>10</v>
@@ -2029,13 +2035,13 @@
         <v>48</v>
       </c>
       <c r="E47" s="22"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="33"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="30"/>
     </row>
     <row r="48" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A48" s="51"/>
+      <c r="A48" s="59"/>
       <c r="B48" s="6"/>
       <c r="C48" s="7" t="s">
         <v>10</v>
@@ -2044,13 +2050,13 @@
         <v>49</v>
       </c>
       <c r="E48" s="22"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="32"/>
-      <c r="I48" s="33"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
+      <c r="I48" s="30"/>
     </row>
     <row r="49" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A49" s="51"/>
+      <c r="A49" s="59"/>
       <c r="B49" s="6"/>
       <c r="C49" s="7" t="s">
         <v>10</v>
@@ -2059,13 +2065,13 @@
         <v>50</v>
       </c>
       <c r="E49" s="22"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32"/>
-      <c r="I49" s="33"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="30"/>
     </row>
     <row r="50" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A50" s="51"/>
+      <c r="A50" s="59"/>
       <c r="B50" s="6"/>
       <c r="C50" s="7" t="s">
         <v>10</v>
@@ -2074,13 +2080,13 @@
         <v>51</v>
       </c>
       <c r="E50" s="22"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="32"/>
-      <c r="I50" s="33"/>
+      <c r="F50" s="29"/>
+      <c r="G50" s="29"/>
+      <c r="H50" s="29"/>
+      <c r="I50" s="30"/>
     </row>
     <row r="51" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A51" s="51"/>
+      <c r="A51" s="59"/>
       <c r="B51" s="6"/>
       <c r="C51" s="7" t="s">
         <v>10</v>
@@ -2089,13 +2095,13 @@
         <v>52</v>
       </c>
       <c r="E51" s="22"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="32"/>
-      <c r="I51" s="33"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="30"/>
     </row>
     <row r="52" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A52" s="51"/>
+      <c r="A52" s="59"/>
       <c r="B52" s="6"/>
       <c r="C52" s="7" t="s">
         <v>10</v>
@@ -2104,13 +2110,13 @@
         <v>53</v>
       </c>
       <c r="E52" s="22"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="32"/>
-      <c r="I52" s="33"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+      <c r="I52" s="30"/>
     </row>
     <row r="53" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A53" s="51"/>
+      <c r="A53" s="59"/>
       <c r="B53" s="6"/>
       <c r="C53" s="15" t="s">
         <v>10</v>
@@ -2119,311 +2125,313 @@
         <v>54</v>
       </c>
       <c r="E53" s="22"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="32"/>
-      <c r="I53" s="33"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="29"/>
+      <c r="I53" s="30"/>
     </row>
     <row r="54" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A54" s="51"/>
+      <c r="A54" s="59"/>
       <c r="B54" s="6"/>
       <c r="C54" s="7"/>
       <c r="D54" s="14"/>
       <c r="E54" s="22"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="32"/>
-      <c r="I54" s="33"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="29"/>
+      <c r="I54" s="30"/>
     </row>
     <row r="55" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A55" s="51"/>
+      <c r="A55" s="59"/>
       <c r="B55" s="6"/>
       <c r="C55" s="17"/>
       <c r="D55" s="18"/>
       <c r="E55" s="22"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="33"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="29"/>
+      <c r="I55" s="30"/>
     </row>
     <row r="56" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A56" s="54" t="s">
+      <c r="A56" s="57" t="s">
         <v>55</v>
       </c>
       <c r="B56" s="6"/>
-      <c r="C56" s="55" t="s">
+      <c r="C56" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="D56" s="55"/>
+      <c r="D56" s="58"/>
       <c r="E56" s="22"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="32"/>
-      <c r="I56" s="33"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="29"/>
+      <c r="I56" s="30"/>
     </row>
     <row r="57" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A57" s="54"/>
+      <c r="A57" s="57"/>
       <c r="B57" s="6"/>
-      <c r="C57" s="55" t="s">
+      <c r="C57" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="D57" s="55"/>
+      <c r="D57" s="58"/>
       <c r="E57" s="22"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="32"/>
-      <c r="I57" s="33"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="29"/>
+      <c r="I57" s="30"/>
     </row>
     <row r="58" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A58" s="54"/>
+      <c r="A58" s="57"/>
       <c r="B58" s="6"/>
-      <c r="C58" s="55" t="s">
+      <c r="C58" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="D58" s="55"/>
+      <c r="D58" s="58"/>
       <c r="E58" s="22"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="32"/>
-      <c r="I58" s="33"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="29"/>
+      <c r="I58" s="30"/>
     </row>
     <row r="59" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A59" s="54"/>
+      <c r="A59" s="57"/>
       <c r="B59" s="13"/>
-      <c r="C59" s="55" t="s">
+      <c r="C59" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="D59" s="55"/>
+      <c r="D59" s="58"/>
       <c r="E59" s="25"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="32"/>
-      <c r="I59" s="33"/>
+      <c r="F59" s="29"/>
+      <c r="G59" s="29"/>
+      <c r="H59" s="29"/>
+      <c r="I59" s="30"/>
     </row>
     <row r="60" spans="1:9" ht="9" customHeight="1">
-      <c r="A60" s="71"/>
+      <c r="A60" s="49"/>
       <c r="B60" s="19"/>
-      <c r="C60" s="73"/>
-      <c r="D60" s="74"/>
+      <c r="C60" s="51"/>
+      <c r="D60" s="52"/>
       <c r="E60" s="24"/>
-      <c r="F60" s="75"/>
-      <c r="G60" s="75"/>
-      <c r="H60" s="75"/>
-      <c r="I60" s="76"/>
+      <c r="F60" s="53"/>
+      <c r="G60" s="53"/>
+      <c r="H60" s="53"/>
+      <c r="I60" s="54"/>
     </row>
     <row r="61" spans="1:9" ht="9" customHeight="1">
-      <c r="A61" s="71"/>
+      <c r="A61" s="49"/>
       <c r="B61" s="19"/>
-      <c r="C61" s="73"/>
-      <c r="D61" s="74"/>
+      <c r="C61" s="51"/>
+      <c r="D61" s="52"/>
       <c r="E61" s="24"/>
-      <c r="F61" s="77"/>
-      <c r="G61" s="77"/>
-      <c r="H61" s="77"/>
-      <c r="I61" s="78"/>
+      <c r="F61" s="55"/>
+      <c r="G61" s="55"/>
+      <c r="H61" s="55"/>
+      <c r="I61" s="56"/>
     </row>
     <row r="62" spans="1:9" ht="9" customHeight="1">
-      <c r="A62" s="71"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="19"/>
-      <c r="C62" s="73"/>
-      <c r="D62" s="74"/>
+      <c r="C62" s="51"/>
+      <c r="D62" s="52"/>
       <c r="E62" s="23"/>
-      <c r="F62" s="56"/>
-      <c r="G62" s="56"/>
-      <c r="H62" s="56"/>
-      <c r="I62" s="57"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="35"/>
+      <c r="I62" s="36"/>
     </row>
     <row r="63" spans="1:9" ht="9" customHeight="1">
-      <c r="A63" s="71"/>
+      <c r="A63" s="49"/>
       <c r="B63" s="19"/>
-      <c r="C63" s="73"/>
-      <c r="D63" s="74"/>
+      <c r="C63" s="51"/>
+      <c r="D63" s="52"/>
       <c r="E63" s="23"/>
-      <c r="F63" s="56"/>
-      <c r="G63" s="56"/>
-      <c r="H63" s="56"/>
-      <c r="I63" s="57"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="35"/>
+      <c r="I63" s="36"/>
     </row>
     <row r="64" spans="1:9" ht="9" customHeight="1">
-      <c r="A64" s="72"/>
+      <c r="A64" s="50"/>
       <c r="B64" s="19"/>
-      <c r="C64" s="73"/>
-      <c r="D64" s="74"/>
+      <c r="C64" s="51"/>
+      <c r="D64" s="52"/>
       <c r="E64" s="23"/>
-      <c r="F64" s="56"/>
-      <c r="G64" s="56"/>
-      <c r="H64" s="56"/>
-      <c r="I64" s="57"/>
+      <c r="F64" s="35"/>
+      <c r="G64" s="35"/>
+      <c r="H64" s="35"/>
+      <c r="I64" s="36"/>
     </row>
     <row r="65" spans="1:9" ht="9" customHeight="1">
-      <c r="A65" s="58" t="s">
+      <c r="A65" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="B65" s="59"/>
-      <c r="C65" s="59"/>
-      <c r="D65" s="60"/>
-      <c r="E65" s="67" t="s">
+      <c r="B65" s="38"/>
+      <c r="C65" s="38"/>
+      <c r="D65" s="39"/>
+      <c r="E65" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="F65" s="67"/>
-      <c r="G65" s="67"/>
-      <c r="H65" s="67"/>
-      <c r="I65" s="68"/>
+      <c r="F65" s="46"/>
+      <c r="G65" s="46"/>
+      <c r="H65" s="46"/>
+      <c r="I65" s="47"/>
     </row>
     <row r="66" spans="1:9" ht="9" customHeight="1">
-      <c r="A66" s="61"/>
-      <c r="B66" s="62"/>
-      <c r="C66" s="62"/>
-      <c r="D66" s="63"/>
-      <c r="E66" s="48" t="s">
+      <c r="A66" s="40"/>
+      <c r="B66" s="41"/>
+      <c r="C66" s="41"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="F66" s="52"/>
+      <c r="G66" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="F66" s="48"/>
-      <c r="G66" s="48"/>
-      <c r="H66" s="48"/>
+      <c r="H66" s="52"/>
       <c r="I66" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="9" customHeight="1">
-      <c r="A67" s="61"/>
-      <c r="B67" s="62"/>
-      <c r="C67" s="62"/>
-      <c r="D67" s="63"/>
-      <c r="E67" s="69"/>
-      <c r="F67" s="69"/>
-      <c r="G67" s="69"/>
-      <c r="H67" s="69"/>
+      <c r="A67" s="40"/>
+      <c r="B67" s="41"/>
+      <c r="C67" s="41"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="83"/>
+      <c r="F67" s="84"/>
+      <c r="G67" s="51"/>
+      <c r="H67" s="52"/>
       <c r="I67" s="20"/>
     </row>
     <row r="68" spans="1:9" ht="9" customHeight="1">
-      <c r="A68" s="61"/>
-      <c r="B68" s="62"/>
-      <c r="C68" s="62"/>
-      <c r="D68" s="63"/>
-      <c r="E68" s="69"/>
-      <c r="F68" s="69"/>
-      <c r="G68" s="69"/>
-      <c r="H68" s="69"/>
+      <c r="A68" s="40"/>
+      <c r="B68" s="41"/>
+      <c r="C68" s="41"/>
+      <c r="D68" s="42"/>
+      <c r="E68" s="83"/>
+      <c r="F68" s="84"/>
+      <c r="G68" s="51"/>
+      <c r="H68" s="52"/>
       <c r="I68" s="20"/>
     </row>
     <row r="69" spans="1:9" ht="9" customHeight="1">
-      <c r="A69" s="61"/>
-      <c r="B69" s="62"/>
-      <c r="C69" s="62"/>
-      <c r="D69" s="63"/>
-      <c r="E69" s="69"/>
-      <c r="F69" s="69"/>
-      <c r="G69" s="69"/>
-      <c r="H69" s="69"/>
+      <c r="A69" s="40"/>
+      <c r="B69" s="41"/>
+      <c r="C69" s="41"/>
+      <c r="D69" s="42"/>
+      <c r="E69" s="83"/>
+      <c r="F69" s="84"/>
+      <c r="G69" s="51"/>
+      <c r="H69" s="52"/>
       <c r="I69" s="20"/>
     </row>
     <row r="70" spans="1:9" ht="9" customHeight="1">
-      <c r="A70" s="61"/>
-      <c r="B70" s="62"/>
-      <c r="C70" s="62"/>
-      <c r="D70" s="63"/>
-      <c r="E70" s="69"/>
-      <c r="F70" s="69"/>
-      <c r="G70" s="69"/>
-      <c r="H70" s="69"/>
+      <c r="A70" s="40"/>
+      <c r="B70" s="41"/>
+      <c r="C70" s="41"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="83"/>
+      <c r="F70" s="84"/>
+      <c r="G70" s="51"/>
+      <c r="H70" s="52"/>
       <c r="I70" s="20"/>
     </row>
     <row r="71" spans="1:9" ht="9" customHeight="1">
-      <c r="A71" s="61"/>
-      <c r="B71" s="62"/>
-      <c r="C71" s="62"/>
-      <c r="D71" s="63"/>
-      <c r="E71" s="69"/>
-      <c r="F71" s="69"/>
-      <c r="G71" s="69"/>
-      <c r="H71" s="69"/>
+      <c r="A71" s="40"/>
+      <c r="B71" s="41"/>
+      <c r="C71" s="41"/>
+      <c r="D71" s="42"/>
+      <c r="E71" s="83"/>
+      <c r="F71" s="84"/>
+      <c r="G71" s="51"/>
+      <c r="H71" s="52"/>
       <c r="I71" s="20"/>
     </row>
     <row r="72" spans="1:9" ht="9" customHeight="1">
-      <c r="A72" s="61"/>
-      <c r="B72" s="62"/>
-      <c r="C72" s="62"/>
-      <c r="D72" s="63"/>
-      <c r="E72" s="70" t="s">
+      <c r="A72" s="40"/>
+      <c r="B72" s="41"/>
+      <c r="C72" s="41"/>
+      <c r="D72" s="42"/>
+      <c r="E72" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="F72" s="70"/>
-      <c r="G72" s="70"/>
-      <c r="H72" s="32"/>
-      <c r="I72" s="33"/>
+      <c r="F72" s="31"/>
+      <c r="G72" s="31"/>
+      <c r="H72" s="29"/>
+      <c r="I72" s="30"/>
     </row>
     <row r="73" spans="1:9" ht="9" customHeight="1">
-      <c r="A73" s="61"/>
-      <c r="B73" s="62"/>
-      <c r="C73" s="62"/>
-      <c r="D73" s="63"/>
-      <c r="E73" s="70" t="s">
+      <c r="A73" s="40"/>
+      <c r="B73" s="41"/>
+      <c r="C73" s="41"/>
+      <c r="D73" s="42"/>
+      <c r="E73" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="F73" s="70"/>
-      <c r="G73" s="70"/>
-      <c r="H73" s="32"/>
-      <c r="I73" s="33"/>
+      <c r="F73" s="31"/>
+      <c r="G73" s="31"/>
+      <c r="H73" s="29"/>
+      <c r="I73" s="30"/>
     </row>
     <row r="74" spans="1:9" ht="9" customHeight="1">
-      <c r="A74" s="61"/>
-      <c r="B74" s="62"/>
-      <c r="C74" s="62"/>
-      <c r="D74" s="63"/>
-      <c r="E74" s="70" t="s">
+      <c r="A74" s="40"/>
+      <c r="B74" s="41"/>
+      <c r="C74" s="41"/>
+      <c r="D74" s="42"/>
+      <c r="E74" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="F74" s="70"/>
-      <c r="G74" s="70"/>
-      <c r="H74" s="32"/>
-      <c r="I74" s="33"/>
+      <c r="F74" s="31"/>
+      <c r="G74" s="31"/>
+      <c r="H74" s="29"/>
+      <c r="I74" s="30"/>
     </row>
     <row r="75" spans="1:9" ht="9" customHeight="1">
-      <c r="A75" s="61"/>
-      <c r="B75" s="62"/>
-      <c r="C75" s="62"/>
-      <c r="D75" s="63"/>
-      <c r="E75" s="70" t="s">
+      <c r="A75" s="40"/>
+      <c r="B75" s="41"/>
+      <c r="C75" s="41"/>
+      <c r="D75" s="42"/>
+      <c r="E75" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="F75" s="70"/>
-      <c r="G75" s="70"/>
-      <c r="H75" s="32"/>
-      <c r="I75" s="33"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="29"/>
+      <c r="I75" s="30"/>
     </row>
     <row r="76" spans="1:9" ht="9" customHeight="1">
-      <c r="A76" s="61"/>
-      <c r="B76" s="62"/>
-      <c r="C76" s="62"/>
-      <c r="D76" s="63"/>
-      <c r="E76" s="70" t="s">
+      <c r="A76" s="40"/>
+      <c r="B76" s="41"/>
+      <c r="C76" s="41"/>
+      <c r="D76" s="42"/>
+      <c r="E76" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="F76" s="70"/>
-      <c r="G76" s="70"/>
-      <c r="H76" s="32"/>
-      <c r="I76" s="33"/>
+      <c r="F76" s="31"/>
+      <c r="G76" s="31"/>
+      <c r="H76" s="29"/>
+      <c r="I76" s="30"/>
     </row>
     <row r="77" spans="1:9" ht="9" customHeight="1" thickBot="1">
-      <c r="A77" s="64"/>
-      <c r="B77" s="65"/>
-      <c r="C77" s="65"/>
-      <c r="D77" s="66"/>
-      <c r="E77" s="82" t="s">
+      <c r="A77" s="43"/>
+      <c r="B77" s="44"/>
+      <c r="C77" s="44"/>
+      <c r="D77" s="45"/>
+      <c r="E77" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="F77" s="82"/>
-      <c r="G77" s="82"/>
-      <c r="H77" s="80"/>
-      <c r="I77" s="81"/>
+      <c r="F77" s="34"/>
+      <c r="G77" s="34"/>
+      <c r="H77" s="32"/>
+      <c r="I77" s="33"/>
     </row>
     <row r="78" spans="1:9" ht="9" customHeight="1" thickTop="1">
-      <c r="G78" s="79" t="s">
+      <c r="G78" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="H78" s="79"/>
-      <c r="I78" s="79"/>
+      <c r="H78" s="28"/>
+      <c r="I78" s="28"/>
     </row>
     <row r="79" spans="1:9" ht="9" customHeight="1">
       <c r="A79"/>
@@ -2454,36 +2462,76 @@
     <row r="85" customFormat="1"/>
     <row r="86" customFormat="1"/>
   </sheetData>
-  <mergeCells count="114">
-    <mergeCell ref="G78:I78"/>
-    <mergeCell ref="H72:I73"/>
-    <mergeCell ref="E73:G73"/>
-    <mergeCell ref="E74:G74"/>
-    <mergeCell ref="H74:I75"/>
-    <mergeCell ref="E75:G75"/>
-    <mergeCell ref="E76:G76"/>
-    <mergeCell ref="H76:I77"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="F64:I64"/>
-    <mergeCell ref="A65:D77"/>
-    <mergeCell ref="E65:I65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E72:G72"/>
-    <mergeCell ref="A60:A64"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="F61:I61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="F62:I62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="F63:I63"/>
-    <mergeCell ref="C64:D64"/>
+  <mergeCells count="120">
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="A9:A18"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="A19:A32"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F42:I42"/>
+    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="F30:I30"/>
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="F34:I34"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="F55:I55"/>
     <mergeCell ref="A56:A59"/>
     <mergeCell ref="C56:D56"/>
@@ -2508,67 +2556,33 @@
     <mergeCell ref="F47:I47"/>
     <mergeCell ref="F48:I48"/>
     <mergeCell ref="F37:I37"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="F41:I41"/>
-    <mergeCell ref="F42:I42"/>
-    <mergeCell ref="F29:I29"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="F30:I30"/>
-    <mergeCell ref="F31:I31"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="F34:I34"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="F28:I28"/>
-    <mergeCell ref="A19:A32"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="A9:A18"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="F64:I64"/>
+    <mergeCell ref="A65:D77"/>
+    <mergeCell ref="E65:I65"/>
+    <mergeCell ref="E72:G72"/>
+    <mergeCell ref="A60:A64"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="F61:I61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="F62:I62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="G78:I78"/>
+    <mergeCell ref="H72:I73"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="H74:I75"/>
+    <mergeCell ref="E75:G75"/>
+    <mergeCell ref="E76:G76"/>
+    <mergeCell ref="H76:I77"/>
+    <mergeCell ref="E77:G77"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.43263888888888902" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/maintenance/electric_engine.xlsx
+++ b/public/assets/templates/maintenance/electric_engine.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145EF4E8-AA66-429C-A460-869D27E4030F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB196C4-896C-4ABF-943A-CB9C33843819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{7A80608D-5162-4C69-AACA-06EF8CFA5F02}"/>
   </bookViews>
@@ -228,18 +228,9 @@
     <t>Teknisi</t>
   </si>
   <si>
-    <t>Diketahui : Miftah Hasan Fuadi</t>
-  </si>
-  <si>
     <t>Staff Engineering</t>
   </si>
   <si>
-    <t>Diterima</t>
-  </si>
-  <si>
-    <t>Staff User</t>
-  </si>
-  <si>
     <t>FRM/EUT/01/009/011-02</t>
   </si>
   <si>
@@ -268,13 +259,22 @@
   </si>
   <si>
     <t>MID</t>
+  </si>
+  <si>
+    <t>Diketahui : Reja Firmansyah</t>
+  </si>
+  <si>
+    <t>Diperiksa : Miftah Hasan Fuadi</t>
+  </si>
+  <si>
+    <t>Supervisor Engineering</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -283,71 +283,78 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="7"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="7"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="7"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="6"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="7"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -355,7 +362,7 @@
       <sz val="7"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -366,7 +373,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -668,272 +675,343 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{C7E27686-6A80-4F81-AC08-0EEB08AA1033}"/>
     <cellStyle name="Normal_Inspection Test Plan" xfId="1" xr:uid="{369CC05B-C1DF-4D8E-8B53-69F81F95BAE7}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1314,143 +1392,143 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickTop="1">
-      <c r="A1" s="64"/>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="68" t="s">
+      <c r="A1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="69"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="43"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="70" t="s">
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="71"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="45"/>
     </row>
     <row r="3" spans="1:9" ht="10" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="72" t="s">
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="73"/>
-      <c r="G3" s="74" t="s">
+      <c r="F3" s="47"/>
+      <c r="G3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="74"/>
-      <c r="I3" s="75"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="10" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81" t="s">
-        <v>75</v>
-      </c>
-      <c r="F4" s="81"/>
-      <c r="G4" s="74" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" s="74"/>
-      <c r="I4" s="75"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4" s="31"/>
+      <c r="I4" s="32"/>
     </row>
     <row r="5" spans="1:9" ht="10" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" s="81"/>
-      <c r="G5" s="74" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5" s="74"/>
-      <c r="I5" s="75"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="31"/>
+      <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="10" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="72" t="s">
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="73"/>
-      <c r="G6" s="74" t="s">
-        <v>74</v>
-      </c>
-      <c r="H6" s="74"/>
-      <c r="I6" s="75"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" s="31"/>
+      <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9" ht="10" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="76"/>
-      <c r="H7" s="77"/>
-      <c r="I7" s="78"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="50"/>
     </row>
     <row r="8" spans="1:9" s="5" customFormat="1" ht="11" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="79" t="s">
+      <c r="B8" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="79"/>
-      <c r="D8" s="79"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="48" t="s">
+      <c r="F8" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="80"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="53"/>
     </row>
     <row r="9" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A9" s="63" t="s">
+      <c r="A9" s="35" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="6"/>
@@ -1461,13 +1539,13 @@
         <v>11</v>
       </c>
       <c r="E9" s="22"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="30"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="37"/>
     </row>
     <row r="10" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A10" s="63"/>
+      <c r="A10" s="35"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
         <v>10</v>
@@ -1476,13 +1554,13 @@
         <v>12</v>
       </c>
       <c r="E10" s="22"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="30"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="37"/>
     </row>
     <row r="11" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A11" s="63"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7" t="s">
         <v>10</v>
@@ -1491,13 +1569,13 @@
         <v>13</v>
       </c>
       <c r="E11" s="22"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="30"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="37"/>
     </row>
     <row r="12" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A12" s="63"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7" t="s">
         <v>10</v>
@@ -1506,13 +1584,13 @@
         <v>14</v>
       </c>
       <c r="E12" s="22"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="30"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="37"/>
     </row>
     <row r="13" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A13" s="63"/>
+      <c r="A13" s="35"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7" t="s">
         <v>10</v>
@@ -1521,13 +1599,13 @@
         <v>15</v>
       </c>
       <c r="E13" s="22"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="30"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="37"/>
     </row>
     <row r="14" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A14" s="63"/>
+      <c r="A14" s="35"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7" t="s">
         <v>10</v>
@@ -1536,13 +1614,13 @@
         <v>16</v>
       </c>
       <c r="E14" s="22"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="30"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="37"/>
     </row>
     <row r="15" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A15" s="63"/>
+      <c r="A15" s="35"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7" t="s">
         <v>10</v>
@@ -1551,13 +1629,13 @@
         <v>17</v>
       </c>
       <c r="E15" s="22"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="30"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="37"/>
     </row>
     <row r="16" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A16" s="63"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="6"/>
       <c r="C16" s="7" t="s">
         <v>10</v>
@@ -1566,33 +1644,33 @@
         <v>18</v>
       </c>
       <c r="E16" s="22"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="30"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="37"/>
     </row>
     <row r="17" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A17" s="63"/>
+      <c r="A17" s="35"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
       <c r="D17" s="8"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="30"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="37"/>
     </row>
     <row r="18" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A18" s="63"/>
+      <c r="A18" s="35"/>
       <c r="B18" s="6"/>
       <c r="E18" s="22"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="30"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="37"/>
     </row>
     <row r="19" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="56" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="6"/>
@@ -1603,15 +1681,15 @@
         <v>20</v>
       </c>
       <c r="E19" s="22"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="30"/>
-      <c r="L19" s="61"/>
-      <c r="M19" s="61"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="37"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
     </row>
     <row r="20" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A20" s="59"/>
+      <c r="A20" s="56"/>
       <c r="B20" s="6"/>
       <c r="C20" s="7" t="s">
         <v>10</v>
@@ -1620,15 +1698,15 @@
         <v>21</v>
       </c>
       <c r="E20" s="22"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="30"/>
-      <c r="L20" s="62"/>
-      <c r="M20" s="62"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="37"/>
+      <c r="L20" s="58"/>
+      <c r="M20" s="58"/>
     </row>
     <row r="21" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A21" s="59"/>
+      <c r="A21" s="56"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7" t="s">
         <v>10</v>
@@ -1637,15 +1715,15 @@
         <v>22</v>
       </c>
       <c r="E21" s="22"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="30"/>
-      <c r="L21" s="62"/>
-      <c r="M21" s="62"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="37"/>
+      <c r="L21" s="58"/>
+      <c r="M21" s="58"/>
     </row>
     <row r="22" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A22" s="59"/>
+      <c r="A22" s="56"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7" t="s">
         <v>10</v>
@@ -1654,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="E22" s="22"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="30"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="37"/>
     </row>
     <row r="23" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A23" s="59"/>
+      <c r="A23" s="56"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7" t="s">
         <v>10</v>
@@ -1669,13 +1747,13 @@
         <v>24</v>
       </c>
       <c r="E23" s="22"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="30"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="37"/>
     </row>
     <row r="24" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A24" s="59"/>
+      <c r="A24" s="56"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7" t="s">
         <v>10</v>
@@ -1684,13 +1762,13 @@
         <v>25</v>
       </c>
       <c r="E24" s="22"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="30"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="37"/>
     </row>
     <row r="25" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A25" s="59"/>
+      <c r="A25" s="56"/>
       <c r="B25" s="6"/>
       <c r="C25" s="7" t="s">
         <v>10</v>
@@ -1699,15 +1777,15 @@
         <v>26</v>
       </c>
       <c r="E25" s="22"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="30"/>
-      <c r="L25" s="60"/>
-      <c r="M25" s="60"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="37"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="55"/>
     </row>
     <row r="26" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A26" s="59"/>
+      <c r="A26" s="56"/>
       <c r="B26" s="6"/>
       <c r="C26" s="7" t="s">
         <v>10</v>
@@ -1716,15 +1794,15 @@
         <v>27</v>
       </c>
       <c r="E26" s="22"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="30"/>
-      <c r="L26" s="60"/>
-      <c r="M26" s="60"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="37"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="55"/>
     </row>
     <row r="27" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A27" s="59"/>
+      <c r="A27" s="56"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7" t="s">
         <v>10</v>
@@ -1733,13 +1811,13 @@
         <v>28</v>
       </c>
       <c r="E27" s="22"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="30"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="37"/>
     </row>
     <row r="28" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A28" s="59"/>
+      <c r="A28" s="56"/>
       <c r="B28" s="6"/>
       <c r="C28" s="7" t="s">
         <v>10</v>
@@ -1748,13 +1826,13 @@
         <v>29</v>
       </c>
       <c r="E28" s="22"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="30"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="37"/>
     </row>
     <row r="29" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A29" s="59"/>
+      <c r="A29" s="56"/>
       <c r="B29" s="6"/>
       <c r="C29" s="7" t="s">
         <v>10</v>
@@ -1763,15 +1841,15 @@
         <v>30</v>
       </c>
       <c r="E29" s="22"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="30"/>
-      <c r="L29" s="60"/>
-      <c r="M29" s="60"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="36"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="37"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="55"/>
     </row>
     <row r="30" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A30" s="59"/>
+      <c r="A30" s="56"/>
       <c r="B30" s="6"/>
       <c r="C30" s="7" t="s">
         <v>10</v>
@@ -1780,15 +1858,15 @@
         <v>31</v>
       </c>
       <c r="E30" s="22"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="30"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="37"/>
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
     </row>
     <row r="31" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A31" s="59"/>
+      <c r="A31" s="56"/>
       <c r="B31" s="6"/>
       <c r="C31" s="7" t="s">
         <v>10</v>
@@ -1797,24 +1875,24 @@
         <v>32</v>
       </c>
       <c r="E31" s="22"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="30"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="37"/>
       <c r="L31" s="11"/>
       <c r="M31" s="11"/>
     </row>
     <row r="32" spans="1:13" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A32" s="59"/>
+      <c r="A32" s="56"/>
       <c r="B32" s="6"/>
       <c r="E32" s="22"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="30"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="37"/>
     </row>
     <row r="33" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A33" s="59" t="s">
+      <c r="A33" s="56" t="s">
         <v>33</v>
       </c>
       <c r="B33" s="6"/>
@@ -1825,13 +1903,13 @@
         <v>34</v>
       </c>
       <c r="E33" s="22"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="30"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="37"/>
     </row>
     <row r="34" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A34" s="59"/>
+      <c r="A34" s="56"/>
       <c r="B34" s="6"/>
       <c r="C34" s="7" t="s">
         <v>10</v>
@@ -1840,13 +1918,13 @@
         <v>35</v>
       </c>
       <c r="E34" s="22"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="30"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="37"/>
     </row>
     <row r="35" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A35" s="59"/>
+      <c r="A35" s="56"/>
       <c r="B35" s="6"/>
       <c r="C35" s="7" t="s">
         <v>10</v>
@@ -1855,13 +1933,13 @@
         <v>36</v>
       </c>
       <c r="E35" s="22"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="30"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="37"/>
     </row>
     <row r="36" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A36" s="59"/>
+      <c r="A36" s="56"/>
       <c r="B36" s="6"/>
       <c r="C36" s="7" t="s">
         <v>10</v>
@@ -1870,13 +1948,13 @@
         <v>37</v>
       </c>
       <c r="E36" s="22"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="30"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="37"/>
     </row>
     <row r="37" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A37" s="59"/>
+      <c r="A37" s="56"/>
       <c r="B37" s="6"/>
       <c r="C37" s="7" t="s">
         <v>10</v>
@@ -1885,13 +1963,13 @@
         <v>38</v>
       </c>
       <c r="E37" s="22"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="30"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="36"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="37"/>
     </row>
     <row r="38" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A38" s="59"/>
+      <c r="A38" s="56"/>
       <c r="B38" s="6"/>
       <c r="C38" s="7" t="s">
         <v>10</v>
@@ -1900,13 +1978,13 @@
         <v>39</v>
       </c>
       <c r="E38" s="22"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="29"/>
-      <c r="I38" s="30"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="37"/>
     </row>
     <row r="39" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A39" s="59"/>
+      <c r="A39" s="56"/>
       <c r="B39" s="6"/>
       <c r="C39" s="7" t="s">
         <v>10</v>
@@ -1915,13 +1993,13 @@
         <v>40</v>
       </c>
       <c r="E39" s="22"/>
-      <c r="F39" s="29"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29"/>
-      <c r="I39" s="30"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="36"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="37"/>
     </row>
     <row r="40" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A40" s="59"/>
+      <c r="A40" s="56"/>
       <c r="B40" s="13"/>
       <c r="C40" s="7" t="s">
         <v>10</v>
@@ -1930,13 +2008,13 @@
         <v>41</v>
       </c>
       <c r="E40" s="22"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="30"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="37"/>
     </row>
     <row r="41" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A41" s="59"/>
+      <c r="A41" s="56"/>
       <c r="B41" s="13"/>
       <c r="C41" s="7" t="s">
         <v>10</v>
@@ -1945,13 +2023,13 @@
         <v>42</v>
       </c>
       <c r="E41" s="25"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="29"/>
-      <c r="I41" s="30"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="37"/>
     </row>
     <row r="42" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A42" s="59"/>
+      <c r="A42" s="56"/>
       <c r="B42" s="13"/>
       <c r="C42" s="7" t="s">
         <v>10</v>
@@ -1960,13 +2038,13 @@
         <v>43</v>
       </c>
       <c r="E42" s="25"/>
-      <c r="F42" s="29"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29"/>
-      <c r="I42" s="30"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="37"/>
     </row>
     <row r="43" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A43" s="59"/>
+      <c r="A43" s="56"/>
       <c r="B43" s="6"/>
       <c r="C43" s="7" t="s">
         <v>10</v>
@@ -1975,13 +2053,13 @@
         <v>44</v>
       </c>
       <c r="E43" s="22"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="30"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="37"/>
     </row>
     <row r="44" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A44" s="59"/>
+      <c r="A44" s="56"/>
       <c r="B44" s="6"/>
       <c r="C44" s="7" t="s">
         <v>10</v>
@@ -1990,13 +2068,13 @@
         <v>45</v>
       </c>
       <c r="E44" s="22"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="30"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="37"/>
     </row>
     <row r="45" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A45" s="59"/>
+      <c r="A45" s="56"/>
       <c r="B45" s="6"/>
       <c r="C45" s="7" t="s">
         <v>10</v>
@@ -2005,13 +2083,13 @@
         <v>46</v>
       </c>
       <c r="E45" s="22"/>
-      <c r="F45" s="29"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="29"/>
-      <c r="I45" s="30"/>
+      <c r="F45" s="36"/>
+      <c r="G45" s="36"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="37"/>
     </row>
     <row r="46" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A46" s="59"/>
+      <c r="A46" s="56"/>
       <c r="B46" s="6"/>
       <c r="C46" s="7" t="s">
         <v>10</v>
@@ -2020,13 +2098,13 @@
         <v>47</v>
       </c>
       <c r="E46" s="22"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="30"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="37"/>
     </row>
     <row r="47" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A47" s="59"/>
+      <c r="A47" s="56"/>
       <c r="B47" s="6"/>
       <c r="C47" s="7" t="s">
         <v>10</v>
@@ -2035,13 +2113,13 @@
         <v>48</v>
       </c>
       <c r="E47" s="22"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="30"/>
+      <c r="F47" s="36"/>
+      <c r="G47" s="36"/>
+      <c r="H47" s="36"/>
+      <c r="I47" s="37"/>
     </row>
     <row r="48" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A48" s="59"/>
+      <c r="A48" s="56"/>
       <c r="B48" s="6"/>
       <c r="C48" s="7" t="s">
         <v>10</v>
@@ -2050,13 +2128,13 @@
         <v>49</v>
       </c>
       <c r="E48" s="22"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="30"/>
+      <c r="F48" s="36"/>
+      <c r="G48" s="36"/>
+      <c r="H48" s="36"/>
+      <c r="I48" s="37"/>
     </row>
     <row r="49" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A49" s="59"/>
+      <c r="A49" s="56"/>
       <c r="B49" s="6"/>
       <c r="C49" s="7" t="s">
         <v>10</v>
@@ -2065,13 +2143,13 @@
         <v>50</v>
       </c>
       <c r="E49" s="22"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="30"/>
+      <c r="F49" s="36"/>
+      <c r="G49" s="36"/>
+      <c r="H49" s="36"/>
+      <c r="I49" s="37"/>
     </row>
     <row r="50" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A50" s="59"/>
+      <c r="A50" s="56"/>
       <c r="B50" s="6"/>
       <c r="C50" s="7" t="s">
         <v>10</v>
@@ -2080,13 +2158,13 @@
         <v>51</v>
       </c>
       <c r="E50" s="22"/>
-      <c r="F50" s="29"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="29"/>
-      <c r="I50" s="30"/>
+      <c r="F50" s="36"/>
+      <c r="G50" s="36"/>
+      <c r="H50" s="36"/>
+      <c r="I50" s="37"/>
     </row>
     <row r="51" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A51" s="59"/>
+      <c r="A51" s="56"/>
       <c r="B51" s="6"/>
       <c r="C51" s="7" t="s">
         <v>10</v>
@@ -2095,13 +2173,13 @@
         <v>52</v>
       </c>
       <c r="E51" s="22"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="29"/>
-      <c r="H51" s="29"/>
-      <c r="I51" s="30"/>
+      <c r="F51" s="36"/>
+      <c r="G51" s="36"/>
+      <c r="H51" s="36"/>
+      <c r="I51" s="37"/>
     </row>
     <row r="52" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A52" s="59"/>
+      <c r="A52" s="56"/>
       <c r="B52" s="6"/>
       <c r="C52" s="7" t="s">
         <v>10</v>
@@ -2110,13 +2188,13 @@
         <v>53</v>
       </c>
       <c r="E52" s="22"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="30"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="36"/>
+      <c r="H52" s="36"/>
+      <c r="I52" s="37"/>
     </row>
     <row r="53" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A53" s="59"/>
+      <c r="A53" s="56"/>
       <c r="B53" s="6"/>
       <c r="C53" s="15" t="s">
         <v>10</v>
@@ -2125,313 +2203,313 @@
         <v>54</v>
       </c>
       <c r="E53" s="22"/>
-      <c r="F53" s="29"/>
-      <c r="G53" s="29"/>
-      <c r="H53" s="29"/>
-      <c r="I53" s="30"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="36"/>
+      <c r="H53" s="36"/>
+      <c r="I53" s="37"/>
     </row>
     <row r="54" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A54" s="59"/>
+      <c r="A54" s="56"/>
       <c r="B54" s="6"/>
       <c r="C54" s="7"/>
       <c r="D54" s="14"/>
       <c r="E54" s="22"/>
-      <c r="F54" s="29"/>
-      <c r="G54" s="29"/>
-      <c r="H54" s="29"/>
-      <c r="I54" s="30"/>
+      <c r="F54" s="36"/>
+      <c r="G54" s="36"/>
+      <c r="H54" s="36"/>
+      <c r="I54" s="37"/>
     </row>
     <row r="55" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A55" s="59"/>
+      <c r="A55" s="56"/>
       <c r="B55" s="6"/>
       <c r="C55" s="17"/>
       <c r="D55" s="18"/>
       <c r="E55" s="22"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="30"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="36"/>
+      <c r="H55" s="36"/>
+      <c r="I55" s="37"/>
     </row>
     <row r="56" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A56" s="57" t="s">
+      <c r="A56" s="59" t="s">
         <v>55</v>
       </c>
       <c r="B56" s="6"/>
-      <c r="C56" s="58" t="s">
+      <c r="C56" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="D56" s="58"/>
+      <c r="D56" s="60"/>
       <c r="E56" s="22"/>
-      <c r="F56" s="29"/>
-      <c r="G56" s="29"/>
-      <c r="H56" s="29"/>
-      <c r="I56" s="30"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="36"/>
+      <c r="H56" s="36"/>
+      <c r="I56" s="37"/>
     </row>
     <row r="57" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A57" s="57"/>
+      <c r="A57" s="59"/>
       <c r="B57" s="6"/>
-      <c r="C57" s="58" t="s">
+      <c r="C57" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="D57" s="58"/>
+      <c r="D57" s="60"/>
       <c r="E57" s="22"/>
-      <c r="F57" s="29"/>
-      <c r="G57" s="29"/>
-      <c r="H57" s="29"/>
-      <c r="I57" s="30"/>
+      <c r="F57" s="36"/>
+      <c r="G57" s="36"/>
+      <c r="H57" s="36"/>
+      <c r="I57" s="37"/>
     </row>
     <row r="58" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A58" s="57"/>
+      <c r="A58" s="59"/>
       <c r="B58" s="6"/>
-      <c r="C58" s="58" t="s">
+      <c r="C58" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="D58" s="58"/>
+      <c r="D58" s="60"/>
       <c r="E58" s="22"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="30"/>
+      <c r="F58" s="36"/>
+      <c r="G58" s="36"/>
+      <c r="H58" s="36"/>
+      <c r="I58" s="37"/>
     </row>
     <row r="59" spans="1:9" s="9" customFormat="1" ht="9" customHeight="1">
-      <c r="A59" s="57"/>
+      <c r="A59" s="59"/>
       <c r="B59" s="13"/>
-      <c r="C59" s="58" t="s">
+      <c r="C59" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="D59" s="58"/>
+      <c r="D59" s="60"/>
       <c r="E59" s="25"/>
-      <c r="F59" s="29"/>
-      <c r="G59" s="29"/>
-      <c r="H59" s="29"/>
-      <c r="I59" s="30"/>
+      <c r="F59" s="36"/>
+      <c r="G59" s="36"/>
+      <c r="H59" s="36"/>
+      <c r="I59" s="37"/>
     </row>
     <row r="60" spans="1:9" ht="9" customHeight="1">
-      <c r="A60" s="49"/>
+      <c r="A60" s="75"/>
       <c r="B60" s="19"/>
-      <c r="C60" s="51"/>
-      <c r="D60" s="52"/>
+      <c r="C60" s="33"/>
+      <c r="D60" s="34"/>
       <c r="E60" s="24"/>
-      <c r="F60" s="53"/>
-      <c r="G60" s="53"/>
-      <c r="H60" s="53"/>
-      <c r="I60" s="54"/>
+      <c r="F60" s="77"/>
+      <c r="G60" s="77"/>
+      <c r="H60" s="77"/>
+      <c r="I60" s="78"/>
     </row>
     <row r="61" spans="1:9" ht="9" customHeight="1">
-      <c r="A61" s="49"/>
+      <c r="A61" s="75"/>
       <c r="B61" s="19"/>
-      <c r="C61" s="51"/>
-      <c r="D61" s="52"/>
+      <c r="C61" s="33"/>
+      <c r="D61" s="34"/>
       <c r="E61" s="24"/>
-      <c r="F61" s="55"/>
-      <c r="G61" s="55"/>
-      <c r="H61" s="55"/>
-      <c r="I61" s="56"/>
+      <c r="F61" s="79"/>
+      <c r="G61" s="79"/>
+      <c r="H61" s="79"/>
+      <c r="I61" s="80"/>
     </row>
     <row r="62" spans="1:9" ht="9" customHeight="1">
-      <c r="A62" s="49"/>
+      <c r="A62" s="75"/>
       <c r="B62" s="19"/>
-      <c r="C62" s="51"/>
-      <c r="D62" s="52"/>
+      <c r="C62" s="33"/>
+      <c r="D62" s="34"/>
       <c r="E62" s="23"/>
-      <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="35"/>
-      <c r="I62" s="36"/>
+      <c r="F62" s="61"/>
+      <c r="G62" s="61"/>
+      <c r="H62" s="61"/>
+      <c r="I62" s="62"/>
     </row>
     <row r="63" spans="1:9" ht="9" customHeight="1">
-      <c r="A63" s="49"/>
+      <c r="A63" s="75"/>
       <c r="B63" s="19"/>
-      <c r="C63" s="51"/>
-      <c r="D63" s="52"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="34"/>
       <c r="E63" s="23"/>
-      <c r="F63" s="35"/>
-      <c r="G63" s="35"/>
-      <c r="H63" s="35"/>
-      <c r="I63" s="36"/>
+      <c r="F63" s="61"/>
+      <c r="G63" s="61"/>
+      <c r="H63" s="61"/>
+      <c r="I63" s="62"/>
     </row>
     <row r="64" spans="1:9" ht="9" customHeight="1">
-      <c r="A64" s="50"/>
+      <c r="A64" s="76"/>
       <c r="B64" s="19"/>
-      <c r="C64" s="51"/>
-      <c r="D64" s="52"/>
+      <c r="C64" s="33"/>
+      <c r="D64" s="34"/>
       <c r="E64" s="23"/>
-      <c r="F64" s="35"/>
-      <c r="G64" s="35"/>
-      <c r="H64" s="35"/>
-      <c r="I64" s="36"/>
+      <c r="F64" s="61"/>
+      <c r="G64" s="61"/>
+      <c r="H64" s="61"/>
+      <c r="I64" s="62"/>
     </row>
     <row r="65" spans="1:9" ht="9" customHeight="1">
-      <c r="A65" s="37" t="s">
+      <c r="A65" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="B65" s="38"/>
-      <c r="C65" s="38"/>
-      <c r="D65" s="39"/>
-      <c r="E65" s="46" t="s">
+      <c r="B65" s="64"/>
+      <c r="C65" s="64"/>
+      <c r="D65" s="65"/>
+      <c r="E65" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="F65" s="46"/>
-      <c r="G65" s="46"/>
-      <c r="H65" s="46"/>
-      <c r="I65" s="47"/>
+      <c r="F65" s="72"/>
+      <c r="G65" s="72"/>
+      <c r="H65" s="72"/>
+      <c r="I65" s="73"/>
     </row>
     <row r="66" spans="1:9" ht="9" customHeight="1">
-      <c r="A66" s="40"/>
-      <c r="B66" s="41"/>
-      <c r="C66" s="41"/>
-      <c r="D66" s="42"/>
-      <c r="E66" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="F66" s="52"/>
-      <c r="G66" s="51" t="s">
+      <c r="A66" s="66"/>
+      <c r="B66" s="67"/>
+      <c r="C66" s="67"/>
+      <c r="D66" s="68"/>
+      <c r="E66" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="F66" s="34"/>
+      <c r="G66" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="H66" s="52"/>
+      <c r="H66" s="34"/>
       <c r="I66" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="9" customHeight="1">
-      <c r="A67" s="40"/>
-      <c r="B67" s="41"/>
-      <c r="C67" s="41"/>
-      <c r="D67" s="42"/>
-      <c r="E67" s="83"/>
-      <c r="F67" s="84"/>
-      <c r="G67" s="51"/>
-      <c r="H67" s="52"/>
+      <c r="A67" s="66"/>
+      <c r="B67" s="67"/>
+      <c r="C67" s="67"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="29"/>
+      <c r="G67" s="33"/>
+      <c r="H67" s="34"/>
       <c r="I67" s="20"/>
     </row>
     <row r="68" spans="1:9" ht="9" customHeight="1">
-      <c r="A68" s="40"/>
-      <c r="B68" s="41"/>
-      <c r="C68" s="41"/>
-      <c r="D68" s="42"/>
-      <c r="E68" s="83"/>
-      <c r="F68" s="84"/>
-      <c r="G68" s="51"/>
-      <c r="H68" s="52"/>
+      <c r="A68" s="66"/>
+      <c r="B68" s="67"/>
+      <c r="C68" s="67"/>
+      <c r="D68" s="68"/>
+      <c r="E68" s="28"/>
+      <c r="F68" s="29"/>
+      <c r="G68" s="33"/>
+      <c r="H68" s="34"/>
       <c r="I68" s="20"/>
     </row>
     <row r="69" spans="1:9" ht="9" customHeight="1">
-      <c r="A69" s="40"/>
-      <c r="B69" s="41"/>
-      <c r="C69" s="41"/>
-      <c r="D69" s="42"/>
-      <c r="E69" s="83"/>
-      <c r="F69" s="84"/>
-      <c r="G69" s="51"/>
-      <c r="H69" s="52"/>
+      <c r="A69" s="66"/>
+      <c r="B69" s="67"/>
+      <c r="C69" s="67"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="33"/>
+      <c r="H69" s="34"/>
       <c r="I69" s="20"/>
     </row>
     <row r="70" spans="1:9" ht="9" customHeight="1">
-      <c r="A70" s="40"/>
-      <c r="B70" s="41"/>
-      <c r="C70" s="41"/>
-      <c r="D70" s="42"/>
-      <c r="E70" s="83"/>
-      <c r="F70" s="84"/>
-      <c r="G70" s="51"/>
-      <c r="H70" s="52"/>
+      <c r="A70" s="66"/>
+      <c r="B70" s="67"/>
+      <c r="C70" s="67"/>
+      <c r="D70" s="68"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="29"/>
+      <c r="G70" s="33"/>
+      <c r="H70" s="34"/>
       <c r="I70" s="20"/>
     </row>
     <row r="71" spans="1:9" ht="9" customHeight="1">
-      <c r="A71" s="40"/>
-      <c r="B71" s="41"/>
-      <c r="C71" s="41"/>
-      <c r="D71" s="42"/>
-      <c r="E71" s="83"/>
-      <c r="F71" s="84"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="52"/>
+      <c r="A71" s="66"/>
+      <c r="B71" s="67"/>
+      <c r="C71" s="67"/>
+      <c r="D71" s="68"/>
+      <c r="E71" s="28"/>
+      <c r="F71" s="29"/>
+      <c r="G71" s="33"/>
+      <c r="H71" s="34"/>
       <c r="I71" s="20"/>
     </row>
     <row r="72" spans="1:9" ht="9" customHeight="1">
-      <c r="A72" s="40"/>
-      <c r="B72" s="41"/>
-      <c r="C72" s="41"/>
-      <c r="D72" s="42"/>
-      <c r="E72" s="31" t="s">
+      <c r="A72" s="66"/>
+      <c r="B72" s="67"/>
+      <c r="C72" s="67"/>
+      <c r="D72" s="68"/>
+      <c r="E72" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="F72" s="31"/>
-      <c r="G72" s="31"/>
-      <c r="H72" s="29"/>
-      <c r="I72" s="30"/>
+      <c r="F72" s="74"/>
+      <c r="G72" s="74"/>
+      <c r="H72" s="36"/>
+      <c r="I72" s="37"/>
     </row>
     <row r="73" spans="1:9" ht="9" customHeight="1">
-      <c r="A73" s="40"/>
-      <c r="B73" s="41"/>
-      <c r="C73" s="41"/>
-      <c r="D73" s="42"/>
-      <c r="E73" s="31" t="s">
+      <c r="A73" s="66"/>
+      <c r="B73" s="67"/>
+      <c r="C73" s="67"/>
+      <c r="D73" s="68"/>
+      <c r="E73" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="F73" s="31"/>
-      <c r="G73" s="31"/>
-      <c r="H73" s="29"/>
-      <c r="I73" s="30"/>
+      <c r="F73" s="74"/>
+      <c r="G73" s="74"/>
+      <c r="H73" s="36"/>
+      <c r="I73" s="37"/>
     </row>
     <row r="74" spans="1:9" ht="9" customHeight="1">
-      <c r="A74" s="40"/>
-      <c r="B74" s="41"/>
-      <c r="C74" s="41"/>
-      <c r="D74" s="42"/>
-      <c r="E74" s="31" t="s">
+      <c r="A74" s="66"/>
+      <c r="B74" s="67"/>
+      <c r="C74" s="67"/>
+      <c r="D74" s="68"/>
+      <c r="E74" s="86" t="s">
+        <v>78</v>
+      </c>
+      <c r="F74" s="86"/>
+      <c r="G74" s="86"/>
+      <c r="H74" s="36"/>
+      <c r="I74" s="37"/>
+    </row>
+    <row r="75" spans="1:9" ht="9" customHeight="1">
+      <c r="A75" s="66"/>
+      <c r="B75" s="67"/>
+      <c r="C75" s="67"/>
+      <c r="D75" s="68"/>
+      <c r="E75" s="74" t="s">
         <v>66</v>
       </c>
-      <c r="F74" s="31"/>
-      <c r="G74" s="31"/>
-      <c r="H74" s="29"/>
-      <c r="I74" s="30"/>
-    </row>
-    <row r="75" spans="1:9" ht="9" customHeight="1">
-      <c r="A75" s="40"/>
-      <c r="B75" s="41"/>
-      <c r="C75" s="41"/>
-      <c r="D75" s="42"/>
-      <c r="E75" s="31" t="s">
+      <c r="F75" s="74"/>
+      <c r="G75" s="74"/>
+      <c r="H75" s="36"/>
+      <c r="I75" s="37"/>
+    </row>
+    <row r="76" spans="1:9" ht="9" customHeight="1">
+      <c r="A76" s="66"/>
+      <c r="B76" s="67"/>
+      <c r="C76" s="67"/>
+      <c r="D76" s="68"/>
+      <c r="E76" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="F76" s="84"/>
+      <c r="G76" s="84"/>
+      <c r="H76" s="36"/>
+      <c r="I76" s="37"/>
+    </row>
+    <row r="77" spans="1:9" ht="9" customHeight="1" thickBot="1">
+      <c r="A77" s="69"/>
+      <c r="B77" s="70"/>
+      <c r="C77" s="70"/>
+      <c r="D77" s="71"/>
+      <c r="E77" s="87" t="s">
+        <v>79</v>
+      </c>
+      <c r="F77" s="85"/>
+      <c r="G77" s="88"/>
+      <c r="H77" s="82"/>
+      <c r="I77" s="83"/>
+    </row>
+    <row r="78" spans="1:9" ht="9" customHeight="1" thickTop="1">
+      <c r="G78" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="F75" s="31"/>
-      <c r="G75" s="31"/>
-      <c r="H75" s="29"/>
-      <c r="I75" s="30"/>
-    </row>
-    <row r="76" spans="1:9" ht="9" customHeight="1">
-      <c r="A76" s="40"/>
-      <c r="B76" s="41"/>
-      <c r="C76" s="41"/>
-      <c r="D76" s="42"/>
-      <c r="E76" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="F76" s="31"/>
-      <c r="G76" s="31"/>
-      <c r="H76" s="29"/>
-      <c r="I76" s="30"/>
-    </row>
-    <row r="77" spans="1:9" ht="9" customHeight="1" thickBot="1">
-      <c r="A77" s="43"/>
-      <c r="B77" s="44"/>
-      <c r="C77" s="44"/>
-      <c r="D77" s="45"/>
-      <c r="E77" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="F77" s="34"/>
-      <c r="G77" s="34"/>
-      <c r="H77" s="32"/>
-      <c r="I77" s="33"/>
-    </row>
-    <row r="78" spans="1:9" ht="9" customHeight="1" thickTop="1">
-      <c r="G78" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="H78" s="28"/>
-      <c r="I78" s="28"/>
+      <c r="H78" s="81"/>
+      <c r="I78" s="81"/>
     </row>
     <row r="79" spans="1:9" ht="9" customHeight="1">
       <c r="A79"/>
@@ -2463,100 +2541,15 @@
     <row r="86" customFormat="1"/>
   </sheetData>
   <mergeCells count="120">
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="A9:A18"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="F28:I28"/>
-    <mergeCell ref="A19:A32"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="F41:I41"/>
-    <mergeCell ref="F42:I42"/>
-    <mergeCell ref="F29:I29"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="F30:I30"/>
-    <mergeCell ref="F31:I31"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="F34:I34"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="A56:A59"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="F59:I59"/>
-    <mergeCell ref="A33:A55"/>
-    <mergeCell ref="F49:I49"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="F43:I43"/>
-    <mergeCell ref="F44:I44"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="F47:I47"/>
-    <mergeCell ref="F48:I48"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="F64:I64"/>
+    <mergeCell ref="G78:I78"/>
+    <mergeCell ref="H72:I73"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="H74:I75"/>
+    <mergeCell ref="E75:G75"/>
+    <mergeCell ref="H76:I77"/>
+    <mergeCell ref="E76:G76"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="E77:G77"/>
     <mergeCell ref="A65:D77"/>
     <mergeCell ref="E65:I65"/>
     <mergeCell ref="E72:G72"/>
@@ -2574,15 +2567,100 @@
     <mergeCell ref="G69:H69"/>
     <mergeCell ref="G70:H70"/>
     <mergeCell ref="G71:H71"/>
-    <mergeCell ref="G78:I78"/>
-    <mergeCell ref="H72:I73"/>
-    <mergeCell ref="E73:G73"/>
-    <mergeCell ref="E74:G74"/>
-    <mergeCell ref="H74:I75"/>
-    <mergeCell ref="E75:G75"/>
-    <mergeCell ref="E76:G76"/>
-    <mergeCell ref="H76:I77"/>
-    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="A33:A55"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="F43:I43"/>
+    <mergeCell ref="F44:I44"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="F46:I46"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="A56:A59"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="A19:A32"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="F30:I30"/>
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="A9:A18"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F42:I42"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="F34:I34"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="F64:I64"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.43263888888888902" bottom="0" header="0" footer="0"/>
